--- a/database/event/3833/event_3833_evp_summary.xlsx
+++ b/database/event/3833/event_3833_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0.5719</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3719</v>
+        <v>2.3108</v>
       </c>
       <c r="E2" t="n">
         <v>6.9145</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5696</v>
+        <v>5.8455</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4607</v>
+        <v>0.4835</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8286</v>
+        <v>1.8849</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5696</v>
+        <v>5.8455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9802999999999999</v>
+        <v>3.7895</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5892</v>
+        <v>2.056</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9802999999999999</v>
+        <v>3.7895</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7946</v>
+        <v>3.0715</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5892</v>
+        <v>2.056</v>
       </c>
       <c r="K3" t="n">
         <v>104</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3838</v>
+        <v>5.1275</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5316</v>
+        <v>5.5696</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4575</v>
+        <v>0.4607</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8133</v>
+        <v>1.775</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5316</v>
+        <v>5.5696</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4756</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>2.056</v>
+        <v>4.5892</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4756</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.817</v>
+        <v>0.7946</v>
       </c>
       <c r="J4" t="n">
-        <v>2.056</v>
+        <v>4.5892</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>4.873</v>
+        <v>5.3838</v>
       </c>
       <c r="N4" t="n">
         <v>190</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9115</v>
+        <v>4.9543</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4063</v>
+        <v>0.4098</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5628</v>
+        <v>1.5299</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9115</v>
+        <v>4.9543</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4017</v>
+        <v>3.4445</v>
       </c>
       <c r="G5" t="n">
         <v>1.5098</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4017</v>
+        <v>3.4445</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7572</v>
+        <v>2.7919</v>
       </c>
       <c r="J5" t="n">
         <v>1.5098</v>
@@ -667,7 +667,7 @@
         <v>150</v>
       </c>
       <c r="M5" t="n">
-        <v>4.267</v>
+        <v>4.3017</v>
       </c>
       <c r="N5" t="n">
         <v>219</v>
@@ -686,7 +686,7 @@
         <v>0.3529</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3022</v>
+        <v>1.2559</v>
       </c>
       <c r="E6" t="n">
         <v>4.2666</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8601</v>
+        <v>4.0287</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3193</v>
+        <v>0.3332</v>
       </c>
       <c r="D7" t="n">
-        <v>1.138</v>
+        <v>1.1611</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8601</v>
+        <v>4.0287</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2029</v>
+        <v>4.0913</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3428</v>
+        <v>-0.0626</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3487</v>
+        <v>4.0913</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5247</v>
+        <v>3.3161</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3428</v>
+        <v>-0.0626</v>
       </c>
       <c r="K7" t="n">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="L7" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1819</v>
+        <v>3.2535</v>
       </c>
       <c r="N7" t="n">
-        <v>251</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8408</v>
+        <v>3.8601</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3177</v>
+        <v>0.3193</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1302</v>
+        <v>1.094</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8408</v>
+        <v>3.8601</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2397</v>
+        <v>4.2029</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3989</v>
+        <v>-0.3428</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4969</v>
+        <v>4.3487</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6448</v>
+        <v>3.5247</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3989</v>
+        <v>-0.3428</v>
       </c>
       <c r="K8" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L8" t="n">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2459</v>
+        <v>3.1819</v>
       </c>
       <c r="N8" t="n">
-        <v>189</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8339</v>
+        <v>3.8408</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3171</v>
+        <v>0.3177</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1274</v>
+        <v>1.0863</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8339</v>
+        <v>3.8408</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8965</v>
+        <v>4.2397</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0626</v>
+        <v>-0.3989</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8965</v>
+        <v>4.4969</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1582</v>
+        <v>3.6448</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0626</v>
+        <v>-0.3989</v>
       </c>
       <c r="K9" t="n">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0956</v>
+        <v>3.2459</v>
       </c>
       <c r="N9" t="n">
-        <v>219</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -870,7 +870,7 @@
         <v>0.2921</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0054</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="E10" t="n">
         <v>3.5319</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3434</v>
+        <v>3.4262</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2765</v>
+        <v>0.2834</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9293</v>
+        <v>0.9211</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3434</v>
+        <v>3.4262</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7401</v>
+        <v>3.8229</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3967</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7401</v>
+        <v>3.8229</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0315</v>
+        <v>3.0986</v>
       </c>
       <c r="J11" t="n">
         <v>-0.3967</v>
@@ -943,7 +943,7 @@
         <v>150</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6348</v>
+        <v>2.7019</v>
       </c>
       <c r="N11" t="n">
         <v>219</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5946</v>
+        <v>2.8974</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2146</v>
+        <v>0.2397</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6268</v>
+        <v>0.7104</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5946</v>
+        <v>2.8974</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9796</v>
+        <v>1.2824</v>
       </c>
       <c r="G12" t="n">
         <v>1.615</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9796</v>
+        <v>1.2824</v>
       </c>
       <c r="I12" t="n">
-        <v>0.794</v>
+        <v>1.0394</v>
       </c>
       <c r="J12" t="n">
         <v>1.615</v>
@@ -989,7 +989,7 @@
         <v>86</v>
       </c>
       <c r="M12" t="n">
-        <v>2.409</v>
+        <v>2.6544</v>
       </c>
       <c r="N12" t="n">
         <v>190</v>
@@ -1008,7 +1008,7 @@
         <v>0.1797</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4562</v>
+        <v>0.4216</v>
       </c>
       <c r="E13" t="n">
         <v>2.1724</v>
@@ -1054,7 +1054,7 @@
         <v>0.122</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1745</v>
+        <v>0.1438</v>
       </c>
       <c r="E14" t="n">
         <v>1.4751</v>
@@ -1100,7 +1100,7 @@
         <v>0.1125</v>
       </c>
       <c r="D15" t="n">
-        <v>0.128</v>
+        <v>0.0979</v>
       </c>
       <c r="E15" t="n">
         <v>1.3599</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7891</v>
+        <v>0.7897</v>
       </c>
       <c r="C16" t="n">
         <v>0.0653</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1026</v>
+        <v>-0.1293</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7891</v>
+        <v>0.7897</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7891</v>
+        <v>0.7897</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7891</v>
+        <v>0.7897</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7891</v>
+        <v>0.7897</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7891</v>
+        <v>0.7897</v>
       </c>
       <c r="N16" t="n">
         <v>158</v>
@@ -1192,7 +1192,7 @@
         <v>0.063</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1136</v>
+        <v>-0.1404</v>
       </c>
       <c r="E17" t="n">
         <v>0.7618</v>
@@ -1238,7 +1238,7 @@
         <v>0.0371</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.24</v>
+        <v>-0.2651</v>
       </c>
       <c r="E18" t="n">
         <v>0.4489</v>
@@ -1274,265 +1274,265 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>Bobosaur</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1549</v>
+        <v>0.1955</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0128</v>
+        <v>0.0162</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3588</v>
+        <v>-0.366</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1549</v>
+        <v>0.1955</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0293</v>
+        <v>0.1955</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8744</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0293</v>
+        <v>0.1955</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8343</v>
+        <v>0.1955</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8744</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="L19" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.04009999999999991</v>
+        <v>0.1955</v>
       </c>
       <c r="N19" t="n">
-        <v>219</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kabal</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1356</v>
+        <v>0.1549</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0112</v>
+        <v>0.0128</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3666</v>
+        <v>-0.3822</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1356</v>
+        <v>0.1549</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1356</v>
+        <v>1.0293</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.8744</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1356</v>
+        <v>1.0293</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1356</v>
+        <v>0.8343</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.8744</v>
       </c>
       <c r="K20" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1356</v>
+        <v>-0.04009999999999991</v>
       </c>
       <c r="N20" t="n">
-        <v>90</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>kabal</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0638</v>
+        <v>0.1356</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0053</v>
+        <v>0.0112</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3956</v>
+        <v>-0.3899</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0638</v>
+        <v>0.1356</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0638</v>
+        <v>0.1356</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0638</v>
+        <v>0.1356</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0638</v>
+        <v>0.1356</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0638</v>
+        <v>0.1356</v>
       </c>
       <c r="N21" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QKA</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0393</v>
+        <v>0.0638</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0033</v>
+        <v>0.0053</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4055</v>
+        <v>-0.4185</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0393</v>
+        <v>0.0638</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0393</v>
+        <v>0.0638</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0393</v>
+        <v>0.0638</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0393</v>
+        <v>0.0638</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0393</v>
+        <v>0.0638</v>
       </c>
       <c r="N22" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>QKA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0053</v>
+        <v>0.0393</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0004</v>
+        <v>0.0033</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4235</v>
+        <v>-0.4283</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0053</v>
+        <v>0.0393</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5236</v>
+        <v>0.0393</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5289</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5236</v>
+        <v>0.0393</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4244</v>
+        <v>0.0393</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5289</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="L23" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1045</v>
+        <v>0.0393</v>
       </c>
       <c r="N23" t="n">
-        <v>189</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0007</v>
+        <v>-0.0004</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4248</v>
+        <v>-0.446</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9915</v>
+        <v>0.5236</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>-0.5289</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9915</v>
+        <v>0.5236</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8036</v>
+        <v>0.4244</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>-0.5289</v>
       </c>
       <c r="K24" t="n">
         <v>146</v>
@@ -1541,7 +1541,7 @@
         <v>43</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1964</v>
+        <v>-0.1045</v>
       </c>
       <c r="N24" t="n">
         <v>189</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bobosaur</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1251</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0103</v>
+        <v>-0.0007</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4719</v>
+        <v>-0.4473</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1251</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1251</v>
+        <v>0.9915</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1251</v>
+        <v>0.9915</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1251</v>
+        <v>0.8036</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K25" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1251</v>
+        <v>-0.1964</v>
       </c>
       <c r="N25" t="n">
-        <v>138</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26">
@@ -1606,7 +1606,7 @@
         <v>-0.0105</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4725</v>
+        <v>-0.4943</v>
       </c>
       <c r="E26" t="n">
         <v>-0.1266</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0155</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4971</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1874</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0203</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5205</v>
+        <v>-0.5417</v>
       </c>
       <c r="E28" t="n">
         <v>-0.2455</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0208</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.523</v>
+        <v>-0.5441</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2515</v>
@@ -1790,7 +1790,7 @@
         <v>-0.028</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5787</v>
       </c>
       <c r="E30" t="n">
         <v>-0.3383</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0348</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5916</v>
+        <v>-0.6118</v>
       </c>
       <c r="E31" t="n">
         <v>-0.4213</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0395</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6141</v>
+        <v>-0.6339</v>
       </c>
       <c r="E32" t="n">
         <v>-0.477</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>ImpressioN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6402</v>
+        <v>-0.5756</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.053</v>
+        <v>-0.0476</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.68</v>
+        <v>-0.6732</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6402</v>
+        <v>-0.5756</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2572</v>
+        <v>-0.5756</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2572</v>
+        <v>-0.5756</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2085</v>
+        <v>-0.5756</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="L33" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5915</v>
+        <v>-0.5756</v>
       </c>
       <c r="N33" t="n">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ImpressioN</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6453</v>
+        <v>-0.6402</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0534</v>
+        <v>-0.053</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.699</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6453</v>
+        <v>-0.6402</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6453</v>
+        <v>-0.2572</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.383</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6453</v>
+        <v>-0.2572</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6453</v>
+        <v>-0.2085</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.383</v>
       </c>
       <c r="K34" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6453</v>
+        <v>-0.5915</v>
       </c>
       <c r="N34" t="n">
-        <v>138</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35">
@@ -2020,7 +2020,7 @@
         <v>-0.0556</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6931</v>
+        <v>-0.7119</v>
       </c>
       <c r="E35" t="n">
         <v>-0.6726</v>
@@ -2066,7 +2066,7 @@
         <v>-0.0769</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7972</v>
+        <v>-0.8145</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9303</v>
@@ -2112,7 +2112,7 @@
         <v>-0.0786</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8052</v>
+        <v>-0.8225</v>
       </c>
       <c r="E37" t="n">
         <v>-0.9502</v>
@@ -2158,7 +2158,7 @@
         <v>-0.0828</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8256</v>
+        <v>-0.8425</v>
       </c>
       <c r="E38" t="n">
         <v>-1.0006</v>
@@ -2204,7 +2204,7 @@
         <v>-0.0857</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.8401</v>
+        <v>-0.8569</v>
       </c>
       <c r="E39" t="n">
         <v>-1.0366</v>
@@ -2250,7 +2250,7 @@
         <v>-0.1007</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9131</v>
+        <v>-0.9288</v>
       </c>
       <c r="E40" t="n">
         <v>-1.2172</v>
@@ -2296,7 +2296,7 @@
         <v>-0.1144</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.98</v>
+        <v>-0.9948</v>
       </c>
       <c r="E41" t="n">
         <v>-1.3828</v>

--- a/database/event/3833/event_3833_evp_summary.xlsx
+++ b/database/event/3833/event_3833_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9145</v>
+        <v>6.6383</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5719</v>
+        <v>0.5491</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3108</v>
+        <v>2.3588</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9145</v>
+        <v>6.6383</v>
       </c>
       <c r="F2" t="n">
-        <v>1.946</v>
+        <v>2.429</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9685</v>
+        <v>4.2093</v>
       </c>
       <c r="H2" t="n">
-        <v>1.946</v>
+        <v>3.0718</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5773</v>
+        <v>1.5972</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9685</v>
+        <v>4.2093</v>
       </c>
       <c r="K2" t="n">
         <v>104</v>
@@ -529,7 +529,7 @@
         <v>86</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5458</v>
+        <v>5.8065</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8455</v>
+        <v>5.9129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4835</v>
+        <v>0.4891</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8849</v>
+        <v>2.0314</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8455</v>
+        <v>5.9129</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7895</v>
+        <v>1.9134</v>
       </c>
       <c r="G3" t="n">
-        <v>2.056</v>
+        <v>3.9995</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7895</v>
+        <v>1.9134</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0715</v>
+        <v>0.9949</v>
       </c>
       <c r="J3" t="n">
-        <v>2.056</v>
+        <v>3.9995</v>
       </c>
       <c r="K3" t="n">
         <v>104</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1275</v>
+        <v>4.9944</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5696</v>
+        <v>5.1839</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4607</v>
+        <v>0.4288</v>
       </c>
       <c r="D4" t="n">
-        <v>1.775</v>
+        <v>1.7023</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5696</v>
+        <v>5.1839</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9802999999999999</v>
+        <v>3.2375</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5892</v>
+        <v>1.9464</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9802999999999999</v>
+        <v>5.9207</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7946</v>
+        <v>3.0785</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5892</v>
+        <v>1.9464</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3838</v>
+        <v>5.0249</v>
       </c>
       <c r="N4" t="n">
         <v>190</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9543</v>
+        <v>4.5987</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4098</v>
+        <v>0.3804</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5299</v>
+        <v>1.4381</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9543</v>
+        <v>4.5987</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4445</v>
+        <v>3.2078</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5098</v>
+        <v>1.3909</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4445</v>
+        <v>5.8161</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7919</v>
+        <v>3.0241</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5098</v>
+        <v>1.3909</v>
       </c>
       <c r="K5" t="n">
         <v>69</v>
@@ -667,7 +667,7 @@
         <v>150</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3017</v>
+        <v>4.415</v>
       </c>
       <c r="N5" t="n">
         <v>219</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2666</v>
+        <v>3.8833</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3529</v>
+        <v>0.3212</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2559</v>
+        <v>1.1151</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2666</v>
+        <v>3.8833</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6129</v>
+        <v>3.227</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6563</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6129</v>
+        <v>5.8836</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9284</v>
+        <v>3.0592</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6563</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>107</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5821</v>
+        <v>3.7155</v>
       </c>
       <c r="N6" t="n">
         <v>251</v>
@@ -722,277 +722,277 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0287</v>
+        <v>3.8109</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3332</v>
+        <v>0.3152</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1611</v>
+        <v>1.0824</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0287</v>
+        <v>3.8109</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0913</v>
+        <v>2.7888</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0626</v>
+        <v>1.0221</v>
       </c>
       <c r="H7" t="n">
-        <v>4.0913</v>
+        <v>4.3396</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3161</v>
+        <v>2.2564</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0626</v>
+        <v>1.0221</v>
       </c>
       <c r="K7" t="n">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="L7" t="n">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2535</v>
+        <v>3.2785</v>
       </c>
       <c r="N7" t="n">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8601</v>
+        <v>3.7952</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3193</v>
+        <v>0.3139</v>
       </c>
       <c r="D8" t="n">
-        <v>1.094</v>
+        <v>1.0753</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8601</v>
+        <v>3.7952</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2029</v>
+        <v>2.1964</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3428</v>
+        <v>1.5988</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3487</v>
+        <v>2.2523</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5247</v>
+        <v>1.1711</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3428</v>
+        <v>1.5988</v>
       </c>
       <c r="K8" t="n">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="L8" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1819</v>
+        <v>2.7699</v>
       </c>
       <c r="N8" t="n">
-        <v>251</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8408</v>
+        <v>3.6739</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3177</v>
+        <v>0.3039</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0863</v>
+        <v>1.0206</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8408</v>
+        <v>3.6739</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2397</v>
+        <v>3.539</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3989</v>
+        <v>0.1349</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4969</v>
+        <v>6.9829</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6448</v>
+        <v>3.6308</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3989</v>
+        <v>0.1349</v>
       </c>
       <c r="K9" t="n">
-        <v>146</v>
+        <v>69</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2459</v>
+        <v>3.7657</v>
       </c>
       <c r="N9" t="n">
-        <v>189</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5319</v>
+        <v>3.524</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2921</v>
+        <v>0.2915</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9529</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5319</v>
+        <v>3.524</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5331</v>
+        <v>3.8237</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9988</v>
+        <v>-0.2997</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5331</v>
+        <v>7.9859</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0531</v>
+        <v>4.1523</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9988</v>
+        <v>-0.2997</v>
       </c>
       <c r="K10" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L10" t="n">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0519</v>
+        <v>3.8526</v>
       </c>
       <c r="N10" t="n">
-        <v>251</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4262</v>
+        <v>3.4106</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2834</v>
+        <v>0.2821</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9211</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4262</v>
+        <v>3.4106</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8229</v>
+        <v>3.5266</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3967</v>
+        <v>-0.116</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8229</v>
+        <v>6.9393</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0986</v>
+        <v>3.6081</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3967</v>
+        <v>-0.116</v>
       </c>
       <c r="K11" t="n">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="L11" t="n">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7019</v>
+        <v>3.4921</v>
       </c>
       <c r="N11" t="n">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8974</v>
+        <v>3.2686</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2397</v>
+        <v>0.2704</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7104</v>
+        <v>0.8376</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8974</v>
+        <v>3.2686</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2824</v>
+        <v>3.4224</v>
       </c>
       <c r="G12" t="n">
-        <v>1.615</v>
+        <v>-0.1538</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2824</v>
+        <v>6.5719</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0394</v>
+        <v>3.4171</v>
       </c>
       <c r="J12" t="n">
-        <v>1.615</v>
+        <v>-0.1538</v>
       </c>
       <c r="K12" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="L12" t="n">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6544</v>
+        <v>3.2633</v>
       </c>
       <c r="N12" t="n">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1724</v>
+        <v>2.3924</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1797</v>
+        <v>0.1979</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4216</v>
+        <v>0.442</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1724</v>
+        <v>2.3924</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7707</v>
+        <v>2.8276</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.4352</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7707</v>
+        <v>4.4764</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2457</v>
+        <v>2.3275</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.4352</v>
       </c>
       <c r="K13" t="n">
         <v>146</v>
@@ -1035,7 +1035,7 @@
         <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6474</v>
+        <v>1.8923</v>
       </c>
       <c r="N13" t="n">
         <v>189</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4751</v>
+        <v>2.1623</v>
       </c>
       <c r="C14" t="n">
-        <v>0.122</v>
+        <v>0.1789</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1438</v>
+        <v>0.3382</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4751</v>
+        <v>2.1623</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2686</v>
+        <v>2.1759</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7437</v>
+        <v>-0.0136</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2686</v>
+        <v>2.1802</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0282</v>
+        <v>1.1336</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7437</v>
+        <v>-0.0136</v>
       </c>
       <c r="K14" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="L14" t="n">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7155</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3599</v>
+        <v>1.314</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1125</v>
+        <v>0.1087</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0979</v>
+        <v>-0.0448</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3599</v>
+        <v>1.314</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1038</v>
+        <v>2.185</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2561</v>
+        <v>-0.871</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1038</v>
+        <v>2.2123</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8947000000000001</v>
+        <v>1.1503</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2561</v>
+        <v>-0.871</v>
       </c>
       <c r="K15" t="n">
         <v>69</v>
@@ -1127,7 +1127,7 @@
         <v>150</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1508</v>
+        <v>0.2793000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>219</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7897</v>
+        <v>1.2697</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0653</v>
+        <v>0.105</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1293</v>
+        <v>-0.0648</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7897</v>
+        <v>1.2697</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7897</v>
+        <v>1.2697</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7897</v>
+        <v>1.2697</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7897</v>
+        <v>1.2697</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7897</v>
+        <v>1.2697</v>
       </c>
       <c r="N16" t="n">
         <v>158</v>
@@ -1182,78 +1182,78 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7618</v>
+        <v>1.2333</v>
       </c>
       <c r="C17" t="n">
-        <v>0.063</v>
+        <v>0.102</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1404</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7618</v>
+        <v>1.2333</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7618</v>
+        <v>2.1949</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.9616</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7618</v>
+        <v>2.2473</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7618</v>
+        <v>1.1685</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.9616</v>
       </c>
       <c r="K17" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7618</v>
+        <v>0.2069000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4489</v>
+        <v>1.1402</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0371</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2651</v>
+        <v>-0.1233</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4489</v>
+        <v>1.1402</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4489</v>
+        <v>1.1402</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4489</v>
+        <v>1.1402</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4489</v>
+        <v>1.1402</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4489</v>
+        <v>1.1402</v>
       </c>
       <c r="N18" t="n">
         <v>158</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bobosaur</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1955</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0162</v>
+        <v>0.0818</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.366</v>
+        <v>-0.1918</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1955</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1955</v>
+        <v>1.3761</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.3877</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1955</v>
+        <v>1.3761</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1955</v>
+        <v>0.7155</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.3877</v>
       </c>
       <c r="K19" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1955</v>
+        <v>0.3278</v>
       </c>
       <c r="N19" t="n">
-        <v>138</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1549</v>
+        <v>0.9565</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0128</v>
+        <v>0.0791</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3822</v>
+        <v>-0.2062</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1549</v>
+        <v>0.9565</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0293</v>
+        <v>0.9565</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8744</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0293</v>
+        <v>0.9565</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8343</v>
+        <v>0.9565</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8744</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="L20" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.04009999999999991</v>
+        <v>0.9565</v>
       </c>
       <c r="N20" t="n">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kabal</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1356</v>
+        <v>0.912</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0112</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3899</v>
+        <v>-0.2263</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1356</v>
+        <v>0.912</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1356</v>
+        <v>-1.6805</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.5925</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1356</v>
+        <v>-1.6805</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1356</v>
+        <v>-0.8738</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.5925</v>
       </c>
       <c r="K21" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1356</v>
+        <v>1.7187</v>
       </c>
       <c r="N21" t="n">
-        <v>90</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0638</v>
+        <v>0.266</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0053</v>
+        <v>0.022</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4185</v>
+        <v>-0.5179</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0638</v>
+        <v>0.266</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0638</v>
+        <v>0.266</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0638</v>
+        <v>0.266</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0638</v>
+        <v>0.266</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0638</v>
+        <v>0.266</v>
       </c>
       <c r="N22" t="n">
         <v>77</v>
@@ -1458,262 +1458,262 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QKA</t>
+          <t>Bobosaur</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0393</v>
+        <v>0.1997</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0033</v>
+        <v>0.0165</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4283</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0393</v>
+        <v>0.1997</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0393</v>
+        <v>0.1997</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0393</v>
+        <v>0.1997</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0393</v>
+        <v>0.1997</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0393</v>
+        <v>0.1997</v>
       </c>
       <c r="N23" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>kabal</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0053</v>
+        <v>0.1991</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0004</v>
+        <v>0.0165</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.446</v>
+        <v>-0.5481</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0053</v>
+        <v>0.1991</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5236</v>
+        <v>0.1991</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5289</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5236</v>
+        <v>0.1991</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4244</v>
+        <v>0.1991</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5289</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="L24" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1045</v>
+        <v>0.1991</v>
       </c>
       <c r="N24" t="n">
-        <v>189</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0007</v>
+        <v>0.013</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4473</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9915</v>
+        <v>0.1573</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9915</v>
+        <v>0.1573</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8036</v>
+        <v>0.1573</v>
       </c>
       <c r="J25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="L25" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1964</v>
+        <v>0.1573</v>
       </c>
       <c r="N25" t="n">
-        <v>189</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1266</v>
+        <v>0.0977</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0105</v>
+        <v>0.0081</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4943</v>
+        <v>-0.5939</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1266</v>
+        <v>0.0977</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1266</v>
+        <v>0.0977</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1266</v>
+        <v>0.0977</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1266</v>
+        <v>0.0977</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1266</v>
+        <v>0.0977</v>
       </c>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Benkai</t>
+          <t>dobu</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1874</v>
+        <v>0.0738</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0155</v>
+        <v>0.0061</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.6047</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1874</v>
+        <v>0.0738</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1874</v>
+        <v>0.0738</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1874</v>
+        <v>0.0738</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1874</v>
+        <v>0.0738</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1874</v>
+        <v>0.0738</v>
       </c>
       <c r="N27" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dobu</t>
+          <t>QKA</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2455</v>
+        <v>0.0696</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0203</v>
+        <v>0.0058</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5417</v>
+        <v>-0.6066</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2455</v>
+        <v>0.0696</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2455</v>
+        <v>0.0696</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2455</v>
+        <v>0.0696</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2455</v>
+        <v>0.0696</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2455</v>
+        <v>0.0696</v>
       </c>
       <c r="N28" t="n">
         <v>90</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>Benkai</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2515</v>
+        <v>-0.0318</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0208</v>
+        <v>-0.0026</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5441</v>
+        <v>-0.6524</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2515</v>
+        <v>-0.0318</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2515</v>
+        <v>-0.0318</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2515</v>
+        <v>-0.0318</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2515</v>
+        <v>-0.0318</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2515</v>
+        <v>-0.0318</v>
       </c>
       <c r="N29" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DickStacy</t>
+          <t>ImpressioN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3383</v>
+        <v>-0.1722</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.028</v>
+        <v>-0.0142</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5787</v>
+        <v>-0.7158</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3383</v>
+        <v>-0.1722</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3383</v>
+        <v>-0.1722</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3383</v>
+        <v>-0.1722</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3383</v>
+        <v>-0.1722</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3383</v>
+        <v>-0.1722</v>
       </c>
       <c r="N30" t="n">
-        <v>77</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4213</v>
+        <v>-0.1823</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0348</v>
+        <v>-0.0151</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6118</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4213</v>
+        <v>-0.1823</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4213</v>
+        <v>-0.1823</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4213</v>
+        <v>-0.1823</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4213</v>
+        <v>-0.1823</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4213</v>
+        <v>-0.1823</v>
       </c>
       <c r="N31" t="n">
         <v>90</v>
@@ -1872,78 +1872,78 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>splashske</t>
+          <t>DickStacy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.477</v>
+        <v>-0.2191</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0395</v>
+        <v>-0.0181</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6339</v>
+        <v>-0.7369</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.477</v>
+        <v>-0.2191</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.477</v>
+        <v>-0.2191</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.477</v>
+        <v>-0.2191</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.477</v>
+        <v>-0.2191</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.477</v>
+        <v>-0.2191</v>
       </c>
       <c r="N32" t="n">
-        <v>138</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ImpressioN</t>
+          <t>splashske</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5756</v>
+        <v>-0.2931</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0476</v>
+        <v>-0.0242</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6732</v>
+        <v>-0.7703</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5756</v>
+        <v>-0.2931</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5756</v>
+        <v>-0.2931</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5756</v>
+        <v>-0.2931</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5756</v>
+        <v>-0.2931</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5756</v>
+        <v>-0.2931</v>
       </c>
       <c r="N33" t="n">
         <v>138</v>
@@ -1964,185 +1964,185 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>morelz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6402</v>
+        <v>-0.3011</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.053</v>
+        <v>-0.0249</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.699</v>
+        <v>-0.7739</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6402</v>
+        <v>-0.3011</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2572</v>
+        <v>-0.1596</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.383</v>
+        <v>-0.1415</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2572</v>
+        <v>-0.1596</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2085</v>
+        <v>-0.083</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.383</v>
+        <v>-0.1415</v>
       </c>
       <c r="K34" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5915</v>
+        <v>-0.2245</v>
       </c>
       <c r="N34" t="n">
-        <v>189</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>erkaSt</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6726</v>
+        <v>-0.3987</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0556</v>
+        <v>-0.033</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7119</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6726</v>
+        <v>-0.3987</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6726</v>
+        <v>-0.2029</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6726</v>
+        <v>-0.2029</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6726</v>
+        <v>-0.1055</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="K35" t="n">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6726</v>
+        <v>-0.3013</v>
       </c>
       <c r="N35" t="n">
-        <v>77</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>erkaSt</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9303</v>
+        <v>-0.4673</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0769</v>
+        <v>-0.0387</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8145</v>
+        <v>-0.849</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9303</v>
+        <v>-0.4673</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.9002</v>
+        <v>-0.4673</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9699</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.9002</v>
+        <v>-0.4673</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.5402</v>
+        <v>-0.4673</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9699</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="L36" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5703</v>
+        <v>-0.4673</v>
       </c>
       <c r="N36" t="n">
-        <v>251</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>morelz</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9502</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0786</v>
+        <v>-0.0535</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8225</v>
+        <v>-0.93</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9502</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5442</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.406</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5442</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4411</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.406</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="L37" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8471</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>251</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0006</v>
+        <v>-0.6784</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0828</v>
+        <v>-0.0561</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8425</v>
+        <v>-0.9443</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0006</v>
+        <v>-0.6784</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0006</v>
+        <v>-0.6784</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0006</v>
+        <v>-0.6784</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0006</v>
+        <v>-0.6784</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0006</v>
+        <v>-0.6784</v>
       </c>
       <c r="N38" t="n">
         <v>90</v>
@@ -2194,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>malta</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0366</v>
+        <v>-0.9702</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.0857</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.8569</v>
+        <v>-1.076</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0366</v>
+        <v>-0.9702</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0366</v>
+        <v>-0.9702</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0366</v>
+        <v>-0.9702</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0366</v>
+        <v>-0.9702</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0366</v>
+        <v>-0.9702</v>
       </c>
       <c r="N39" t="n">
-        <v>77</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2172</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1007</v>
+        <v>-0.0804</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9288</v>
+        <v>-1.077</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2172</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2172</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2172</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2172</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2172</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3828</v>
+        <v>-1.6054</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1144</v>
+        <v>-0.1328</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.9948</v>
+        <v>-1.3628</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3828</v>
+        <v>-1.6054</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3828</v>
+        <v>-2.4339</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.8285</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3828</v>
+        <v>-2.4339</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3828</v>
+        <v>-1.2655</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.8285</v>
       </c>
       <c r="K41" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3828</v>
+        <v>-0.4370000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>158</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4201</v>
+        <v>0.4759</v>
       </c>
       <c r="J2" t="n">
-        <v>10.5025</v>
+        <v>11.8975</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0585</v>
+        <v>-0.0677</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4625</v>
+        <v>-1.6925</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.323</v>
+        <v>-0.2177</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.074999999999999</v>
+        <v>-5.4425</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.72</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4491</v>
+        <v>-0.2948</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.2275</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7631</v>
+        <v>-0.5188</v>
       </c>
       <c r="J6" t="n">
-        <v>-19.0775</v>
+        <v>-12.97</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2309</v>
+        <v>1.1606</v>
       </c>
       <c r="J7" t="n">
-        <v>30.7725</v>
+        <v>29.015</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1502</v>
+        <v>1.1116</v>
       </c>
       <c r="J8" t="n">
-        <v>28.755</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7508</v>
+        <v>0.8316</v>
       </c>
       <c r="J9" t="n">
-        <v>18.77</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.411</v>
+        <v>0.5064</v>
       </c>
       <c r="J10" t="n">
-        <v>10.275</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.18</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3863</v>
+        <v>0.4813</v>
       </c>
       <c r="J11" t="n">
-        <v>9.657500000000001</v>
+        <v>12.0325</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.99</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1841</v>
+        <v>0.1967</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3138</v>
+        <v>3.5406</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.53</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6081</v>
+        <v>-0.4287</v>
       </c>
       <c r="J13" t="n">
-        <v>-10.9458</v>
+        <v>-7.7166</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.49</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6723</v>
+        <v>-0.4656</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.1014</v>
+        <v>-8.380800000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.47</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7022</v>
+        <v>-0.4844</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.6396</v>
+        <v>-8.719200000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.3</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9318</v>
+        <v>-0.6489</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.7724</v>
+        <v>-11.6802</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.43</v>
       </c>
       <c r="I17" t="n">
-        <v>2.312</v>
+        <v>1.8681</v>
       </c>
       <c r="J17" t="n">
-        <v>41.616</v>
+        <v>33.6258</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.85</v>
       </c>
       <c r="I18" t="n">
-        <v>1.685</v>
+        <v>1.4728</v>
       </c>
       <c r="J18" t="n">
-        <v>30.33</v>
+        <v>26.5104</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.65</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3034</v>
+        <v>1.2528</v>
       </c>
       <c r="J19" t="n">
-        <v>23.4612</v>
+        <v>22.5504</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.31</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5944</v>
+        <v>0.7323</v>
       </c>
       <c r="J20" t="n">
-        <v>10.6992</v>
+        <v>13.1814</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4235</v>
+        <v>-0.3394</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.623</v>
+        <v>-6.1092</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.43</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0587</v>
+        <v>0.769</v>
       </c>
       <c r="J22" t="n">
-        <v>25.4088</v>
+        <v>18.456</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.42</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0376</v>
+        <v>0.7562</v>
       </c>
       <c r="J23" t="n">
-        <v>24.9024</v>
+        <v>18.1488</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6661</v>
+        <v>0.5453</v>
       </c>
       <c r="J24" t="n">
-        <v>15.9864</v>
+        <v>13.0872</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.15</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3556</v>
+        <v>0.3897</v>
       </c>
       <c r="J25" t="n">
-        <v>8.5344</v>
+        <v>9.3528</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3722</v>
+        <v>-0.2926</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.9328</v>
+        <v>-7.0224</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2226</v>
+        <v>0.2157</v>
       </c>
       <c r="J27" t="n">
-        <v>5.3424</v>
+        <v>5.1768</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.98</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0216</v>
+        <v>-0.0144</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5184</v>
+        <v>-0.3456</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3765</v>
+        <v>-0.2478</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.036</v>
+        <v>-5.9472</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.73</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4372</v>
+        <v>-0.2863</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.4928</v>
+        <v>-6.8712</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5894</v>
+        <v>-0.3905</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.1456</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.9</v>
       </c>
       <c r="I32" t="n">
-        <v>1.8057</v>
+        <v>1.3054</v>
       </c>
       <c r="J32" t="n">
-        <v>34.3083</v>
+        <v>24.8026</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.66</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4475</v>
+        <v>1.0254</v>
       </c>
       <c r="J33" t="n">
-        <v>27.5025</v>
+        <v>19.4826</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4476</v>
+        <v>0.4606</v>
       </c>
       <c r="J34" t="n">
-        <v>8.5044</v>
+        <v>8.7514</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1415</v>
+        <v>0.2323</v>
       </c>
       <c r="J35" t="n">
-        <v>2.6885</v>
+        <v>4.4137</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0083</v>
+        <v>0.0771</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.1577</v>
+        <v>1.4649</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0224</v>
+        <v>-0.0519</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4256</v>
+        <v>-0.9861</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0917</v>
+        <v>-0.1014</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.7423</v>
+        <v>-1.9266</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.57</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6056</v>
+        <v>-0.4115</v>
       </c>
       <c r="J39" t="n">
-        <v>-11.5064</v>
+        <v>-7.8185</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6199</v>
+        <v>-0.4208</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.7781</v>
+        <v>-7.9952</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.4</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8308</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.7852</v>
+        <v>-10.8509</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5908</v>
+        <v>0.4623</v>
       </c>
       <c r="J42" t="n">
-        <v>24.8136</v>
+        <v>19.4166</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.11</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3973</v>
+        <v>0.3514</v>
       </c>
       <c r="J43" t="n">
-        <v>16.6866</v>
+        <v>14.7588</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.08</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3039</v>
+        <v>0.278</v>
       </c>
       <c r="J44" t="n">
-        <v>12.7638</v>
+        <v>11.676</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.05</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1972</v>
+        <v>0.1874</v>
       </c>
       <c r="J45" t="n">
-        <v>8.282400000000001</v>
+        <v>7.8708</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.708</v>
+        <v>-0.6595</v>
       </c>
       <c r="J46" t="n">
-        <v>-29.736</v>
+        <v>-27.699</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4698</v>
+        <v>0.4693</v>
       </c>
       <c r="J47" t="n">
-        <v>19.7316</v>
+        <v>19.7106</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2975</v>
+        <v>0.3462</v>
       </c>
       <c r="J48" t="n">
-        <v>12.495</v>
+        <v>14.5404</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.13</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2304</v>
+        <v>0.2827</v>
       </c>
       <c r="J49" t="n">
-        <v>9.6768</v>
+        <v>11.8734</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0921</v>
+        <v>0.1447</v>
       </c>
       <c r="J50" t="n">
-        <v>3.8682</v>
+        <v>6.0774</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2241</v>
+        <v>-0.1239</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.4122</v>
+        <v>-5.2038</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3693</v>
+        <v>0.317</v>
       </c>
       <c r="J52" t="n">
-        <v>9.2325</v>
+        <v>7.925</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.08</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2093</v>
+        <v>0.1651</v>
       </c>
       <c r="J53" t="n">
-        <v>5.2325</v>
+        <v>4.1275</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0356</v>
+        <v>-0.033</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.89</v>
+        <v>-0.825</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2477</v>
+        <v>-0.1514</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.1925</v>
+        <v>-3.785</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5514</v>
+        <v>-0.3597</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.785</v>
+        <v>-8.9925</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.62</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8319</v>
+        <v>0.5787</v>
       </c>
       <c r="J57" t="n">
-        <v>20.7975</v>
+        <v>14.4675</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3298</v>
+        <v>0.3039</v>
       </c>
       <c r="J58" t="n">
-        <v>8.244999999999999</v>
+        <v>7.5975</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.14</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1959</v>
+        <v>0.205</v>
       </c>
       <c r="J59" t="n">
-        <v>4.8975</v>
+        <v>5.125</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.13</v>
       </c>
       <c r="I60" t="n">
-        <v>0.18</v>
+        <v>0.1917</v>
       </c>
       <c r="J60" t="n">
-        <v>4.5</v>
+        <v>4.7925</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1531</v>
+        <v>-0.0716</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.8275</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.44</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0888</v>
+        <v>0.7856</v>
       </c>
       <c r="J62" t="n">
-        <v>43.552</v>
+        <v>31.424</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.35</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8944</v>
+        <v>0.668</v>
       </c>
       <c r="J63" t="n">
-        <v>35.776</v>
+        <v>26.72</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6538</v>
+        <v>0.5337</v>
       </c>
       <c r="J64" t="n">
-        <v>26.152</v>
+        <v>21.348</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.07</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1373</v>
+        <v>0.2096</v>
       </c>
       <c r="J65" t="n">
-        <v>5.492</v>
+        <v>8.384</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1312</v>
+        <v>-0.0541</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.248</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.23</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4386</v>
+        <v>0.4355</v>
       </c>
       <c r="J67" t="n">
-        <v>17.544</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.012</v>
+        <v>-0.018</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.48</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1595</v>
+        <v>-0.0964</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.38</v>
+        <v>-3.856</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.85</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2987</v>
+        <v>-0.1838</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.948</v>
+        <v>-7.352</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.345</v>
+        <v>-0.2146</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.8</v>
+        <v>-8.584</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.03</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1107</v>
+        <v>0.1</v>
       </c>
       <c r="J72" t="n">
-        <v>4.5387</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0261</v>
+        <v>0.0061</v>
       </c>
       <c r="J73" t="n">
-        <v>1.0701</v>
+        <v>0.2501</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.062</v>
+        <v>-0.0472</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.542</v>
+        <v>-1.9352</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1372</v>
+        <v>-0.0843</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.6252</v>
+        <v>-3.4563</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2814</v>
+        <v>-0.1728</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.5374</v>
+        <v>-7.0848</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.47</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1787</v>
+        <v>1.1112</v>
       </c>
       <c r="J77" t="n">
-        <v>48.3267</v>
+        <v>45.5592</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.18</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5049</v>
+        <v>0.5171</v>
       </c>
       <c r="J78" t="n">
-        <v>20.7009</v>
+        <v>21.2011</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5049</v>
+        <v>0.5171</v>
       </c>
       <c r="J79" t="n">
-        <v>20.7009</v>
+        <v>21.2011</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.194</v>
+        <v>0.2529</v>
       </c>
       <c r="J80" t="n">
-        <v>7.954</v>
+        <v>10.3689</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.92</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4087</v>
+        <v>-0.3358</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.7567</v>
+        <v>-13.7678</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>0.203</v>
+        <v>0.2028</v>
       </c>
       <c r="J82" t="n">
-        <v>5.278</v>
+        <v>5.2728</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1241</v>
+        <v>0.1082</v>
       </c>
       <c r="J83" t="n">
-        <v>3.2266</v>
+        <v>2.8132</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.03</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1241</v>
+        <v>0.1082</v>
       </c>
       <c r="J84" t="n">
-        <v>3.2266</v>
+        <v>2.8132</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2701</v>
+        <v>-0.1691</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.0226</v>
+        <v>-4.3966</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.65</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5714</v>
+        <v>-0.3749</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.8564</v>
+        <v>-9.747400000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>1.286</v>
+        <v>1.1799</v>
       </c>
       <c r="J87" t="n">
-        <v>33.436</v>
+        <v>30.6774</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7725</v>
+        <v>0.7611</v>
       </c>
       <c r="J88" t="n">
-        <v>20.085</v>
+        <v>19.7886</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1384</v>
+        <v>0.1958</v>
       </c>
       <c r="J89" t="n">
-        <v>3.5984</v>
+        <v>5.0908</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.02</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0026</v>
+        <v>0.0595</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.06759999999999999</v>
+        <v>1.547</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5158</v>
+        <v>-0.4483</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.4108</v>
+        <v>-11.6558</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.52</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7942</v>
+        <v>0.9878</v>
       </c>
       <c r="J92" t="n">
-        <v>21.4434</v>
+        <v>26.6706</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1833</v>
+        <v>0.1888</v>
       </c>
       <c r="J93" t="n">
-        <v>4.9491</v>
+        <v>5.0976</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3029</v>
+        <v>-0.1854</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.1783</v>
+        <v>-5.0058</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3184</v>
+        <v>-0.1958</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.5968</v>
+        <v>-5.2866</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.61</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6303</v>
+        <v>-0.4177</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.0181</v>
+        <v>-11.2779</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.892</v>
+        <v>0.8809</v>
       </c>
       <c r="J97" t="n">
-        <v>24.084</v>
+        <v>23.7843</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>16.3161</v>
+        <v>16.0731</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.15</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4336</v>
+        <v>0.4464</v>
       </c>
       <c r="J99" t="n">
-        <v>11.7072</v>
+        <v>12.0528</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2988</v>
+        <v>0.3428</v>
       </c>
       <c r="J100" t="n">
-        <v>8.067600000000001</v>
+        <v>9.255599999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4011</v>
+        <v>-0.33</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.8297</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4938</v>
+        <v>0.5777</v>
       </c>
       <c r="J102" t="n">
-        <v>12.345</v>
+        <v>14.4425</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0859</v>
+        <v>-0.0696</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.1475</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.92</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.156</v>
+        <v>-0.1043</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.9</v>
+        <v>-2.6075</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3173</v>
+        <v>-0.1996</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.9325</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5576</v>
+        <v>-0.365</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.94</v>
+        <v>-9.125</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8423</v>
+        <v>0.8315</v>
       </c>
       <c r="J107" t="n">
-        <v>21.0575</v>
+        <v>20.7875</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7487</v>
+        <v>0.7375</v>
       </c>
       <c r="J108" t="n">
-        <v>18.7175</v>
+        <v>18.4375</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5724</v>
+        <v>0.5689</v>
       </c>
       <c r="J109" t="n">
-        <v>14.31</v>
+        <v>14.2225</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4881</v>
+        <v>0.4949</v>
       </c>
       <c r="J110" t="n">
-        <v>12.2025</v>
+        <v>12.3725</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6935</v>
+        <v>-0.6374</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.3375</v>
+        <v>-15.935</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>1.042</v>
+        <v>1.0239</v>
       </c>
       <c r="J112" t="n">
-        <v>23.966</v>
+        <v>23.5497</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6249</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>14.3727</v>
+        <v>14.5498</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.19</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5067</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J114" t="n">
-        <v>11.6541</v>
+        <v>12.3694</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.07</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1513</v>
+        <v>0.2173</v>
       </c>
       <c r="J115" t="n">
-        <v>3.4799</v>
+        <v>4.9979</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.05</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0877</v>
+        <v>0.1548</v>
       </c>
       <c r="J116" t="n">
-        <v>2.0171</v>
+        <v>3.5604</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.04</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1606</v>
+        <v>0.145</v>
       </c>
       <c r="J117" t="n">
-        <v>3.6938</v>
+        <v>3.335</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.93</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1087</v>
+        <v>-0.09</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.5001</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.85</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2709</v>
+        <v>-0.1752</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.2307</v>
+        <v>-4.0296</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.288</v>
+        <v>-0.1854</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.624</v>
+        <v>-4.2642</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3676</v>
+        <v>-0.2355</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.454800000000001</v>
+        <v>-5.4165</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0373</v>
+        <v>1.0168</v>
       </c>
       <c r="J122" t="n">
-        <v>29.0444</v>
+        <v>28.4704</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.929</v>
+        <v>0.9211</v>
       </c>
       <c r="J123" t="n">
-        <v>26.012</v>
+        <v>25.7908</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6209</v>
+        <v>0.6161</v>
       </c>
       <c r="J124" t="n">
-        <v>17.3852</v>
+        <v>17.2508</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.12</v>
       </c>
       <c r="I125" t="n">
-        <v>0.319</v>
+        <v>0.3669</v>
       </c>
       <c r="J125" t="n">
-        <v>8.932</v>
+        <v>10.2732</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9466</v>
+        <v>-0.9151</v>
       </c>
       <c r="J126" t="n">
-        <v>-26.5048</v>
+        <v>-25.6228</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4602</v>
+        <v>0.5316</v>
       </c>
       <c r="J127" t="n">
-        <v>12.8856</v>
+        <v>14.8848</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.95</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0674</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.1112</v>
+        <v>-1.8872</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1163</v>
+        <v>-0.0915</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.2564</v>
+        <v>-2.562</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.73</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.459</v>
+        <v>-0.2959</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.852</v>
+        <v>-8.2852</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5271</v>
+        <v>-0.3437</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.7588</v>
+        <v>-9.6236</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3102</v>
+        <v>0.3398</v>
       </c>
       <c r="J132" t="n">
-        <v>9.305999999999999</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0067</v>
+        <v>-0.017</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.201</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.92</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1743</v>
+        <v>-0.1069</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.229</v>
+        <v>-3.207</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.88</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2463</v>
+        <v>-0.1509</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.389</v>
+        <v>-4.527</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.84</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3114</v>
+        <v>-0.1929</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.342000000000001</v>
+        <v>-5.787</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.53</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3129</v>
+        <v>1.1969</v>
       </c>
       <c r="J137" t="n">
-        <v>39.387</v>
+        <v>35.907</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.52</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2932</v>
+        <v>1.184</v>
       </c>
       <c r="J138" t="n">
-        <v>38.796</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3989</v>
+        <v>-0.3284</v>
       </c>
       <c r="J139" t="n">
-        <v>-11.967</v>
+        <v>-9.852</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5379</v>
+        <v>-0.4726</v>
       </c>
       <c r="J140" t="n">
-        <v>-16.137</v>
+        <v>-14.178</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.85</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5899</v>
+        <v>-0.5274</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.697</v>
+        <v>-15.822</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4407</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>14.9838</v>
+        <v>17.2924</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.08</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2093</v>
+        <v>0.2157</v>
       </c>
       <c r="J143" t="n">
-        <v>7.1162</v>
+        <v>7.3338</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.99</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0174</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.2992</v>
+        <v>-0.5916</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.136</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.624</v>
+        <v>-2.8594</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.55</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7</v>
+        <v>-0.4704</v>
       </c>
       <c r="J146" t="n">
-        <v>-23.8</v>
+        <v>-15.9936</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7534</v>
+        <v>0.74</v>
       </c>
       <c r="J147" t="n">
-        <v>25.6156</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6555</v>
+        <v>0.644</v>
       </c>
       <c r="J148" t="n">
-        <v>22.287</v>
+        <v>21.896</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6301</v>
+        <v>0.6197</v>
       </c>
       <c r="J149" t="n">
-        <v>21.4234</v>
+        <v>21.0698</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.12</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3296</v>
+        <v>0.3697</v>
       </c>
       <c r="J150" t="n">
-        <v>11.2064</v>
+        <v>12.5698</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5132</v>
+        <v>-0.4462</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.4488</v>
+        <v>-15.1708</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.91</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0183</v>
+        <v>-0.0487</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.366</v>
+        <v>-0.974</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.7</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3555</v>
+        <v>-0.2848</v>
       </c>
       <c r="J153" t="n">
-        <v>-7.11</v>
+        <v>-5.696</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.61</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5198</v>
+        <v>-0.3679</v>
       </c>
       <c r="J154" t="n">
-        <v>-10.396</v>
+        <v>-7.358</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.4695</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.76</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.4</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8209</v>
+        <v>-0.5642</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.418</v>
+        <v>-11.284</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.89</v>
       </c>
       <c r="I157" t="n">
-        <v>1.82</v>
+        <v>1.5466</v>
       </c>
       <c r="J157" t="n">
-        <v>36.4</v>
+        <v>30.932</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.63</v>
       </c>
       <c r="I158" t="n">
-        <v>1.3509</v>
+        <v>1.2486</v>
       </c>
       <c r="J158" t="n">
-        <v>27.018</v>
+        <v>24.972</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.53</v>
       </c>
       <c r="I159" t="n">
-        <v>1.1498</v>
+        <v>1.1314</v>
       </c>
       <c r="J159" t="n">
-        <v>22.996</v>
+        <v>22.628</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.36</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7543</v>
+        <v>0.8754</v>
       </c>
       <c r="J160" t="n">
-        <v>15.086</v>
+        <v>17.508</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4258</v>
+        <v>-0.342</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.516</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.92</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0037</v>
+        <v>-0.0381</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.0851</v>
+        <v>-0.8763</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.71</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.3433</v>
+        <v>-0.2762</v>
       </c>
       <c r="J163" t="n">
-        <v>-7.8959</v>
+        <v>-6.3526</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.63</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4833</v>
+        <v>-0.3513</v>
       </c>
       <c r="J164" t="n">
-        <v>-11.1159</v>
+        <v>-8.0799</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.53</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.6481</v>
+        <v>-0.4424</v>
       </c>
       <c r="J165" t="n">
-        <v>-14.9063</v>
+        <v>-10.1752</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.36</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8727</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>-20.0721</v>
+        <v>-13.8759</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.84</v>
       </c>
       <c r="I167" t="n">
-        <v>1.7243</v>
+        <v>1.4853</v>
       </c>
       <c r="J167" t="n">
-        <v>39.6589</v>
+        <v>34.1619</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.71</v>
       </c>
       <c r="I168" t="n">
-        <v>1.4913</v>
+        <v>1.3374</v>
       </c>
       <c r="J168" t="n">
-        <v>34.2999</v>
+        <v>30.7602</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7013</v>
+        <v>0.827</v>
       </c>
       <c r="J169" t="n">
-        <v>16.1299</v>
+        <v>19.021</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.29</v>
       </c>
       <c r="I170" t="n">
-        <v>0.5919</v>
+        <v>0.7145</v>
       </c>
       <c r="J170" t="n">
-        <v>13.6137</v>
+        <v>16.4335</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.29</v>
       </c>
       <c r="I171" t="n">
-        <v>0.5919</v>
+        <v>0.7145</v>
       </c>
       <c r="J171" t="n">
-        <v>13.6137</v>
+        <v>16.4335</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.2</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4195</v>
+        <v>0.3649</v>
       </c>
       <c r="J172" t="n">
-        <v>10.4875</v>
+        <v>9.1225</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.02</v>
       </c>
       <c r="I173" t="n">
-        <v>0.113</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>2.825</v>
+        <v>1.715</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3557</v>
+        <v>-0.2269</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.8925</v>
+        <v>-5.6725</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.75</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4296</v>
+        <v>-0.2761</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.74</v>
+        <v>-6.9025</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4579</v>
+        <v>-0.2954</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.4475</v>
+        <v>-7.385</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.39</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5707</v>
+        <v>0.5013</v>
       </c>
       <c r="J177" t="n">
-        <v>14.2675</v>
+        <v>12.5325</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5707</v>
+        <v>0.5013</v>
       </c>
       <c r="J178" t="n">
-        <v>14.2675</v>
+        <v>12.5325</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1184</v>
+        <v>0.1376</v>
       </c>
       <c r="J179" t="n">
-        <v>2.96</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.08</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1013</v>
+        <v>0.1229</v>
       </c>
       <c r="J180" t="n">
-        <v>2.5325</v>
+        <v>3.0725</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.06</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0659</v>
+        <v>0.0924</v>
       </c>
       <c r="J181" t="n">
-        <v>1.6475</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5914</v>
+        <v>1.3876</v>
       </c>
       <c r="J182" t="n">
-        <v>41.3764</v>
+        <v>36.0776</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0894</v>
+        <v>1.0693</v>
       </c>
       <c r="J183" t="n">
-        <v>28.3244</v>
+        <v>27.8018</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.41</v>
       </c>
       <c r="I184" t="n">
-        <v>0.9827</v>
+        <v>0.9981</v>
       </c>
       <c r="J184" t="n">
-        <v>25.5502</v>
+        <v>25.9506</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.01</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0992</v>
+        <v>-0.0188</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.5792</v>
+        <v>-0.4888</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4483</v>
+        <v>-0.3691</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.6558</v>
+        <v>-9.5966</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.88</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1486</v>
+        <v>-0.1309</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.8636</v>
+        <v>-3.4034</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.82</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2515</v>
+        <v>-0.1945</v>
       </c>
       <c r="J188" t="n">
-        <v>-6.539</v>
+        <v>-5.057</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3065</v>
+        <v>-0.2237</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.969</v>
+        <v>-5.8162</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4334</v>
+        <v>-0.2893</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.2684</v>
+        <v>-7.5218</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.71</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4487</v>
+        <v>-0.2988</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.6662</v>
+        <v>-7.7688</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7313</v>
+        <v>0.698</v>
       </c>
       <c r="J192" t="n">
-        <v>19.7451</v>
+        <v>18.846</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.16</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5279</v>
+        <v>0.4939</v>
       </c>
       <c r="J193" t="n">
-        <v>14.2533</v>
+        <v>13.3353</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.355</v>
+        <v>0.3313</v>
       </c>
       <c r="J194" t="n">
-        <v>9.585000000000001</v>
+        <v>8.9451</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.06</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2159</v>
+        <v>0.2155</v>
       </c>
       <c r="J195" t="n">
-        <v>5.8293</v>
+        <v>5.8185</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.73</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8546</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>-23.0742</v>
+        <v>-22.032</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6586</v>
+        <v>0.8079</v>
       </c>
       <c r="J197" t="n">
-        <v>17.7822</v>
+        <v>21.8133</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.32</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5225</v>
+        <v>0.6262</v>
       </c>
       <c r="J198" t="n">
-        <v>14.1075</v>
+        <v>16.9074</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.91</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2311</v>
+        <v>-0.1309</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.2397</v>
+        <v>-3.5343</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2311</v>
+        <v>-0.1309</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.2397</v>
+        <v>-3.5343</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.79</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4127</v>
+        <v>-0.257</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.1429</v>
+        <v>-6.939</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4681</v>
+        <v>0.5429</v>
       </c>
       <c r="J202" t="n">
-        <v>12.1706</v>
+        <v>14.1154</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.02</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1047</v>
+        <v>0.0838</v>
       </c>
       <c r="J203" t="n">
-        <v>2.7222</v>
+        <v>2.1788</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1049</v>
+        <v>-0.0814</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.7274</v>
+        <v>-2.1164</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.83</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3159</v>
+        <v>-0.1991</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.2134</v>
+        <v>-5.1766</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6701</v>
+        <v>-0.448</v>
       </c>
       <c r="J206" t="n">
-        <v>-17.4226</v>
+        <v>-11.648</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.41</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0214</v>
+        <v>1.0141</v>
       </c>
       <c r="J207" t="n">
-        <v>26.5564</v>
+        <v>26.3666</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8213</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>21.3538</v>
+        <v>21.6086</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7497</v>
+        <v>0.763</v>
       </c>
       <c r="J209" t="n">
-        <v>19.4922</v>
+        <v>19.838</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.24</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6192</v>
+        <v>0.6486</v>
       </c>
       <c r="J210" t="n">
-        <v>16.0992</v>
+        <v>16.8636</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.89</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5119</v>
+        <v>-0.4396</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.3094</v>
+        <v>-11.4296</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3654</v>
+        <v>0.4076</v>
       </c>
       <c r="J212" t="n">
-        <v>10.2312</v>
+        <v>11.4128</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1241</v>
+        <v>0.1082</v>
       </c>
       <c r="J213" t="n">
-        <v>3.4748</v>
+        <v>3.0296</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1593</v>
+        <v>-0.1046</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.4604</v>
+        <v>-2.9288</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2866</v>
+        <v>-0.1795</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.024800000000001</v>
+        <v>-5.026</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.67</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5455</v>
+        <v>-0.3561</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.274</v>
+        <v>-9.970800000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.45</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1297</v>
+        <v>1.0812</v>
       </c>
       <c r="J217" t="n">
-        <v>31.6316</v>
+        <v>30.2736</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.29</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7788</v>
+        <v>0.7755</v>
       </c>
       <c r="J218" t="n">
-        <v>21.8064</v>
+        <v>21.714</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.14</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3612</v>
+        <v>0.4149</v>
       </c>
       <c r="J219" t="n">
-        <v>10.1136</v>
+        <v>11.6172</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0156</v>
+        <v>0.0519</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.4368</v>
+        <v>1.4532</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.01</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.0578</v>
+        <v>0.0108</v>
       </c>
       <c r="J221" t="n">
-        <v>-1.6184</v>
+        <v>0.3024</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.21</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6443</v>
+        <v>0.6148</v>
       </c>
       <c r="J222" t="n">
-        <v>18.0404</v>
+        <v>17.2144</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5135</v>
+        <v>0.487</v>
       </c>
       <c r="J223" t="n">
-        <v>14.378</v>
+        <v>13.636</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.16</v>
       </c>
       <c r="I224" t="n">
-        <v>0.5135</v>
+        <v>0.487</v>
       </c>
       <c r="J224" t="n">
-        <v>14.378</v>
+        <v>13.636</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0369</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.2352</v>
+        <v>1.0332</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.86</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5442</v>
+        <v>-0.4844</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.2376</v>
+        <v>-13.5632</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.29</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5967</v>
       </c>
       <c r="J227" t="n">
-        <v>14.126</v>
+        <v>16.7076</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.19</v>
       </c>
       <c r="I228" t="n">
-        <v>0.3663</v>
+        <v>0.4178</v>
       </c>
       <c r="J228" t="n">
-        <v>10.2564</v>
+        <v>11.6984</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2248</v>
+        <v>0.2444</v>
       </c>
       <c r="J229" t="n">
-        <v>6.2944</v>
+        <v>6.8432</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1772</v>
+        <v>-0.1009</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.9616</v>
+        <v>-2.8252</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.73</v>
+        <v>-0.4933</v>
       </c>
       <c r="J231" t="n">
-        <v>-20.44</v>
+        <v>-13.8124</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.51</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2343</v>
+        <v>1.1504</v>
       </c>
       <c r="J232" t="n">
-        <v>32.0918</v>
+        <v>29.9104</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.5</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2143</v>
+        <v>1.1376</v>
       </c>
       <c r="J233" t="n">
-        <v>31.5718</v>
+        <v>29.5776</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1996</v>
+        <v>0.2702</v>
       </c>
       <c r="J234" t="n">
-        <v>5.1896</v>
+        <v>7.0252</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1874</v>
+        <v>-0.1076</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.8724</v>
+        <v>-2.7976</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.99</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1874</v>
+        <v>-0.1076</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.8724</v>
+        <v>-2.7976</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.05</v>
       </c>
       <c r="I237" t="n">
-        <v>0.182</v>
+        <v>0.1707</v>
       </c>
       <c r="J237" t="n">
-        <v>4.732</v>
+        <v>4.4382</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.92</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1263</v>
+        <v>-0.1011</v>
       </c>
       <c r="J238" t="n">
-        <v>-3.2838</v>
+        <v>-2.6286</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1658</v>
+        <v>-0.1233</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.3108</v>
+        <v>-3.2058</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3192</v>
+        <v>-0.2051</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.299200000000001</v>
+        <v>-5.3326</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.74</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4399</v>
+        <v>-0.2839</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.4374</v>
+        <v>-7.3814</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3833/event_3833_evp_summary.xlsx
+++ b/database/event/3833/event_3833_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6383</v>
+        <v>6.6886</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5491</v>
+        <v>0.5532</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3588</v>
+        <v>2.4206</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6383</v>
+        <v>6.6886</v>
       </c>
       <c r="F2" t="n">
-        <v>2.429</v>
+        <v>2.3713</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2093</v>
+        <v>4.3173</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0718</v>
+        <v>2.9297</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5972</v>
+        <v>1.582</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2093</v>
+        <v>4.3173</v>
       </c>
       <c r="K2" t="n">
         <v>104</v>
@@ -529,7 +529,7 @@
         <v>86</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8065</v>
+        <v>5.8993</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9129</v>
+        <v>5.9925</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4891</v>
+        <v>0.4957</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0314</v>
+        <v>2.1037</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9129</v>
+        <v>5.9925</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9134</v>
+        <v>1.7348</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9995</v>
+        <v>4.2577</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9134</v>
+        <v>1.7348</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9949</v>
+        <v>0.9368</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9995</v>
+        <v>4.2577</v>
       </c>
       <c r="K3" t="n">
         <v>104</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9944</v>
+        <v>5.1945</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1839</v>
+        <v>5.2109</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4288</v>
+        <v>0.431</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7023</v>
+        <v>1.7479</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1839</v>
+        <v>5.2109</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2375</v>
+        <v>3.1573</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9464</v>
+        <v>2.0536</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9207</v>
+        <v>5.523</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0785</v>
+        <v>2.9824</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9464</v>
+        <v>2.0536</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0249</v>
+        <v>5.036</v>
       </c>
       <c r="N4" t="n">
         <v>190</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5987</v>
+        <v>4.5899</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3804</v>
+        <v>0.3797</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4381</v>
+        <v>1.4652</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5987</v>
+        <v>4.5899</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2078</v>
+        <v>3.1486</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3909</v>
+        <v>1.4413</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8161</v>
+        <v>5.4942</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0241</v>
+        <v>2.9668</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3909</v>
+        <v>1.4413</v>
       </c>
       <c r="K5" t="n">
         <v>69</v>
@@ -667,7 +667,7 @@
         <v>150</v>
       </c>
       <c r="M5" t="n">
-        <v>4.415</v>
+        <v>4.4081</v>
       </c>
       <c r="N5" t="n">
         <v>219</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8833</v>
+        <v>3.8846</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3212</v>
+        <v>0.3213</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1151</v>
+        <v>1.1441</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8833</v>
+        <v>3.8846</v>
       </c>
       <c r="F6" t="n">
-        <v>3.227</v>
+        <v>3.1596</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6563</v>
+        <v>0.725</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8836</v>
+        <v>5.5306</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0592</v>
+        <v>2.9865</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6563</v>
+        <v>0.725</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>107</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7155</v>
+        <v>3.7115</v>
       </c>
       <c r="N6" t="n">
         <v>251</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8109</v>
+        <v>3.7899</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3152</v>
+        <v>0.3135</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0824</v>
+        <v>1.101</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8109</v>
+        <v>3.7899</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7888</v>
+        <v>2.6966</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0221</v>
+        <v>1.0933</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3396</v>
+        <v>4.0028</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2564</v>
+        <v>2.1615</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0221</v>
+        <v>1.0933</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>107</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2785</v>
+        <v>3.2548</v>
       </c>
       <c r="N7" t="n">
         <v>251</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7952</v>
+        <v>3.7881</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3139</v>
+        <v>0.3133</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0753</v>
+        <v>1.1002</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7952</v>
+        <v>3.7881</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1964</v>
+        <v>2.0513</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5988</v>
+        <v>1.7368</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2523</v>
+        <v>2.0513</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1711</v>
+        <v>1.1077</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5988</v>
+        <v>1.7368</v>
       </c>
       <c r="K8" t="n">
         <v>104</v>
@@ -805,7 +805,7 @@
         <v>86</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7699</v>
+        <v>2.8445</v>
       </c>
       <c r="N8" t="n">
         <v>190</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6739</v>
+        <v>3.6403</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3039</v>
+        <v>0.3011</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0206</v>
+        <v>1.0329</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6739</v>
+        <v>3.6403</v>
       </c>
       <c r="F9" t="n">
-        <v>3.539</v>
+        <v>3.4729</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1349</v>
+        <v>0.1674</v>
       </c>
       <c r="H9" t="n">
-        <v>6.9829</v>
+        <v>6.5642</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6308</v>
+        <v>3.5446</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1349</v>
+        <v>0.1674</v>
       </c>
       <c r="K9" t="n">
         <v>69</v>
@@ -851,7 +851,7 @@
         <v>150</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7657</v>
+        <v>3.712</v>
       </c>
       <c r="N9" t="n">
         <v>219</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.524</v>
+        <v>3.3559</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2915</v>
+        <v>0.2776</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9529</v>
+        <v>0.9035</v>
       </c>
       <c r="E10" t="n">
-        <v>3.524</v>
+        <v>3.3559</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8237</v>
+        <v>3.6984</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2997</v>
+        <v>-0.3425</v>
       </c>
       <c r="H10" t="n">
-        <v>7.9859</v>
+        <v>7.3081</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1523</v>
+        <v>3.9463</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2997</v>
+        <v>-0.3425</v>
       </c>
       <c r="K10" t="n">
         <v>146</v>
@@ -897,7 +897,7 @@
         <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8526</v>
+        <v>3.6038</v>
       </c>
       <c r="N10" t="n">
         <v>189</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4106</v>
+        <v>3.3113</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2821</v>
+        <v>0.2739</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.8832</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4106</v>
+        <v>3.3113</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5266</v>
+        <v>3.4323</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.116</v>
+        <v>-0.121</v>
       </c>
       <c r="H11" t="n">
-        <v>6.9393</v>
+        <v>6.4303</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6081</v>
+        <v>3.4723</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.116</v>
+        <v>-0.121</v>
       </c>
       <c r="K11" t="n">
         <v>144</v>
@@ -943,7 +943,7 @@
         <v>107</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4921</v>
+        <v>3.3513</v>
       </c>
       <c r="N11" t="n">
         <v>251</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2686</v>
+        <v>3.2205</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2704</v>
+        <v>0.2664</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8376</v>
+        <v>0.8418</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2686</v>
+        <v>3.2205</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4224</v>
+        <v>3.3588</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1538</v>
+        <v>-0.1383</v>
       </c>
       <c r="H12" t="n">
-        <v>6.5719</v>
+        <v>6.1877</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4171</v>
+        <v>3.3413</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1538</v>
+        <v>-0.1383</v>
       </c>
       <c r="K12" t="n">
         <v>69</v>
@@ -989,7 +989,7 @@
         <v>150</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2633</v>
+        <v>3.203</v>
       </c>
       <c r="N12" t="n">
         <v>219</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3924</v>
+        <v>2.2707</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1979</v>
+        <v>0.1878</v>
       </c>
       <c r="D13" t="n">
-        <v>0.442</v>
+        <v>0.4095</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3924</v>
+        <v>2.2707</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8276</v>
+        <v>2.7334</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4352</v>
+        <v>-0.4627</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4764</v>
+        <v>4.1243</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3275</v>
+        <v>2.2271</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4352</v>
+        <v>-0.4627</v>
       </c>
       <c r="K13" t="n">
         <v>146</v>
@@ -1035,7 +1035,7 @@
         <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8923</v>
+        <v>1.7644</v>
       </c>
       <c r="N13" t="n">
         <v>189</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1623</v>
+        <v>2.1143</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1789</v>
+        <v>0.1749</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3382</v>
+        <v>0.3383</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1623</v>
+        <v>2.1143</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1759</v>
+        <v>2.0547</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0136</v>
+        <v>0.0596</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1802</v>
+        <v>2.0547</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1336</v>
+        <v>1.1095</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0136</v>
+        <v>0.0596</v>
       </c>
       <c r="K14" t="n">
         <v>69</v>
@@ -1081,7 +1081,7 @@
         <v>150</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.1691</v>
       </c>
       <c r="N14" t="n">
         <v>219</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.314</v>
+        <v>1.3387</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1087</v>
+        <v>0.1107</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0448</v>
+        <v>-0.0148</v>
       </c>
       <c r="E15" t="n">
-        <v>1.314</v>
+        <v>1.3387</v>
       </c>
       <c r="F15" t="n">
-        <v>2.185</v>
+        <v>-1.4308</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.871</v>
+        <v>2.7695</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2123</v>
+        <v>-1.4308</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1503</v>
+        <v>-0.7726</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.871</v>
+        <v>2.7695</v>
       </c>
       <c r="K15" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="L15" t="n">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2793000000000001</v>
+        <v>1.9969</v>
       </c>
       <c r="N15" t="n">
-        <v>219</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2697</v>
+        <v>1.1941</v>
       </c>
       <c r="C16" t="n">
-        <v>0.105</v>
+        <v>0.0988</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0648</v>
+        <v>-0.0806</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2697</v>
+        <v>1.1941</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2697</v>
+        <v>1.1941</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2697</v>
+        <v>1.1941</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2697</v>
+        <v>1.1941</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2697</v>
+        <v>1.1941</v>
       </c>
       <c r="N16" t="n">
         <v>158</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2333</v>
+        <v>1.1225</v>
       </c>
       <c r="C17" t="n">
-        <v>0.102</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.1132</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2333</v>
+        <v>1.1225</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1949</v>
+        <v>2.1032</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9616</v>
+        <v>-0.9807</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2473</v>
+        <v>2.1032</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1685</v>
+        <v>1.1357</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9616</v>
+        <v>-0.9807</v>
       </c>
       <c r="K17" t="n">
         <v>146</v>
@@ -1219,7 +1219,7 @@
         <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2069000000000001</v>
+        <v>0.1549999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>189</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1402</v>
+        <v>1.1156</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1233</v>
+        <v>-0.1164</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1402</v>
+        <v>1.1156</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1402</v>
+        <v>2.0693</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.9537</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1402</v>
+        <v>2.0693</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1402</v>
+        <v>1.1174</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.9537</v>
       </c>
       <c r="K18" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1402</v>
+        <v>0.1637</v>
       </c>
       <c r="N18" t="n">
-        <v>158</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.0493</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0818</v>
+        <v>0.0868</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1918</v>
+        <v>-0.1465</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.0493</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3761</v>
+        <v>1.0493</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3877</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3761</v>
+        <v>1.0493</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7155</v>
+        <v>1.0493</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3877</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="L19" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3278</v>
+        <v>1.0493</v>
       </c>
       <c r="N19" t="n">
-        <v>189</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9565</v>
+        <v>0.9666</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0791</v>
+        <v>0.08</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2062</v>
+        <v>-0.1842</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9565</v>
+        <v>0.9666</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9565</v>
+        <v>1.3967</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.4301</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9565</v>
+        <v>1.3967</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9565</v>
+        <v>0.7542</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.4301</v>
       </c>
       <c r="K20" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9565</v>
+        <v>0.3241</v>
       </c>
       <c r="N20" t="n">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.912</v>
+        <v>0.8738</v>
       </c>
       <c r="C21" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2263</v>
+        <v>-0.2264</v>
       </c>
       <c r="E21" t="n">
-        <v>0.912</v>
+        <v>0.8738</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6805</v>
+        <v>0.8738</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5925</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6805</v>
+        <v>0.8738</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8738</v>
+        <v>0.8738</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5925</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="L21" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7187</v>
+        <v>0.8738</v>
       </c>
       <c r="N21" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.266</v>
+        <v>0.2169</v>
       </c>
       <c r="C22" t="n">
-        <v>0.022</v>
+        <v>0.0179</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5179</v>
+        <v>-0.5255</v>
       </c>
       <c r="E22" t="n">
-        <v>0.266</v>
+        <v>0.2169</v>
       </c>
       <c r="F22" t="n">
-        <v>0.266</v>
+        <v>0.2169</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.266</v>
+        <v>0.2169</v>
       </c>
       <c r="I22" t="n">
-        <v>0.266</v>
+        <v>0.2169</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.266</v>
+        <v>0.2169</v>
       </c>
       <c r="N22" t="n">
         <v>77</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bobosaur</t>
+          <t>kabal</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1997</v>
+        <v>0.1768</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0165</v>
+        <v>0.0146</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5437</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1997</v>
+        <v>0.1768</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1997</v>
+        <v>0.1768</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1997</v>
+        <v>0.1768</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1997</v>
+        <v>0.1768</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1997</v>
+        <v>0.1768</v>
       </c>
       <c r="N23" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kabal</t>
+          <t>Bobosaur</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1991</v>
+        <v>0.1461</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0165</v>
+        <v>0.0121</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5481</v>
+        <v>-0.5577</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1991</v>
+        <v>0.1461</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1991</v>
+        <v>0.1461</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1991</v>
+        <v>0.1461</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1991</v>
+        <v>0.1461</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1991</v>
+        <v>0.1461</v>
       </c>
       <c r="N24" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1573</v>
+        <v>0.1059</v>
       </c>
       <c r="C25" t="n">
-        <v>0.013</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.576</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1573</v>
+        <v>0.1059</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1573</v>
+        <v>0.1059</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1573</v>
+        <v>0.1059</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1573</v>
+        <v>0.1059</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1573</v>
+        <v>0.1059</v>
       </c>
       <c r="N25" t="n">
         <v>77</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0977</v>
+        <v>0.08</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0081</v>
+        <v>0.0066</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5939</v>
+        <v>-0.5878</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0977</v>
+        <v>0.08</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0977</v>
+        <v>0.08</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0977</v>
+        <v>0.08</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0977</v>
+        <v>0.08</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0977</v>
+        <v>0.08</v>
       </c>
       <c r="N26" t="n">
         <v>158</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dobu</t>
+          <t>QKA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0738</v>
+        <v>0.0522</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0061</v>
+        <v>0.0043</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6047</v>
+        <v>-0.6004</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0738</v>
+        <v>0.0522</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0738</v>
+        <v>0.0522</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0738</v>
+        <v>0.0522</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0738</v>
+        <v>0.0522</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0738</v>
+        <v>0.0522</v>
       </c>
       <c r="N27" t="n">
         <v>90</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QKA</t>
+          <t>dobu</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0696</v>
+        <v>0.0307</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0058</v>
+        <v>0.0025</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6066</v>
+        <v>-0.6102</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0696</v>
+        <v>0.0307</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0696</v>
+        <v>0.0307</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0696</v>
+        <v>0.0307</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0696</v>
+        <v>0.0307</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0696</v>
+        <v>0.0307</v>
       </c>
       <c r="N28" t="n">
         <v>90</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0318</v>
+        <v>-0.0785</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0026</v>
+        <v>-0.0065</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6524</v>
+        <v>-0.6599</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0318</v>
+        <v>-0.0785</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0318</v>
+        <v>-0.0785</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0318</v>
+        <v>-0.0785</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0318</v>
+        <v>-0.0785</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0318</v>
+        <v>-0.0785</v>
       </c>
       <c r="N29" t="n">
         <v>138</v>
@@ -1780,170 +1780,170 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ImpressioN</t>
+          <t>xiaosaGe</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1722</v>
+        <v>-0.2092</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0142</v>
+        <v>-0.0173</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7158</v>
+        <v>-0.7194</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1722</v>
+        <v>-0.2092</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1722</v>
+        <v>-0.2092</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1722</v>
+        <v>-0.2092</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1722</v>
+        <v>-0.2092</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1722</v>
+        <v>-0.2092</v>
       </c>
       <c r="N30" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>xiaosaGe</t>
+          <t>DickStacy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1823</v>
+        <v>-0.2453</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0151</v>
+        <v>-0.0203</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.7359</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1823</v>
+        <v>-0.2453</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1823</v>
+        <v>-0.2453</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1823</v>
+        <v>-0.2453</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1823</v>
+        <v>-0.2453</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1823</v>
+        <v>-0.2453</v>
       </c>
       <c r="N31" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DickStacy</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2191</v>
+        <v>-0.2832</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0181</v>
+        <v>-0.0234</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7369</v>
+        <v>-0.7531</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2191</v>
+        <v>-0.2832</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2191</v>
+        <v>-0.0648</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.2184</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2191</v>
+        <v>-0.0648</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2191</v>
+        <v>-0.035</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.2184</v>
       </c>
       <c r="K32" t="n">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2191</v>
+        <v>-0.2534</v>
       </c>
       <c r="N32" t="n">
-        <v>77</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>splashske</t>
+          <t>ImpressioN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2931</v>
+        <v>-0.2867</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0242</v>
+        <v>-0.0237</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7703</v>
+        <v>-0.7547</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2931</v>
+        <v>-0.2867</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2931</v>
+        <v>-0.2867</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2931</v>
+        <v>-0.2867</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2931</v>
+        <v>-0.2867</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2931</v>
+        <v>-0.2867</v>
       </c>
       <c r="N33" t="n">
         <v>138</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3011</v>
+        <v>-0.3149</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0249</v>
+        <v>-0.026</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7739</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3011</v>
+        <v>-0.3149</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1596</v>
+        <v>-0.1689</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1415</v>
+        <v>-0.146</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1596</v>
+        <v>-0.1689</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.083</v>
+        <v>-0.0912</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.1415</v>
+        <v>-0.146</v>
       </c>
       <c r="K34" t="n">
         <v>144</v>
@@ -2001,7 +2001,7 @@
         <v>107</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2245</v>
+        <v>-0.2372</v>
       </c>
       <c r="N34" t="n">
         <v>251</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>splashske</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3987</v>
+        <v>-0.3275</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.033</v>
+        <v>-0.0271</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.7733</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3987</v>
+        <v>-0.3275</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2029</v>
+        <v>-0.3275</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2029</v>
+        <v>-0.3275</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1055</v>
+        <v>-0.3275</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="L35" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3013</v>
+        <v>-0.3275</v>
       </c>
       <c r="N35" t="n">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4673</v>
+        <v>-0.5085</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0387</v>
+        <v>-0.0421</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.849</v>
+        <v>-0.8557</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4673</v>
+        <v>-0.5085</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4673</v>
+        <v>-0.5085</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4673</v>
+        <v>-0.5085</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4673</v>
+        <v>-0.5085</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4673</v>
+        <v>-0.5085</v>
       </c>
       <c r="N36" t="n">
         <v>77</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6679</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0535</v>
+        <v>-0.0552</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.93</v>
+        <v>-0.9282</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6679</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6679</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6679</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6679</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6679</v>
       </c>
       <c r="N37" t="n">
         <v>77</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6784</v>
+        <v>-0.7127</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0561</v>
+        <v>-0.059</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9443</v>
+        <v>-0.9486</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6784</v>
+        <v>-0.7127</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6784</v>
+        <v>-0.7127</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6784</v>
+        <v>-0.7127</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6784</v>
+        <v>-0.7127</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6784</v>
+        <v>-0.7127</v>
       </c>
       <c r="N38" t="n">
         <v>90</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9702</v>
+        <v>-0.988</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.076</v>
+        <v>-1.074</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9702</v>
+        <v>-0.988</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9702</v>
+        <v>-0.988</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9702</v>
+        <v>-0.988</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9702</v>
+        <v>-0.988</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9702</v>
+        <v>-0.988</v>
       </c>
       <c r="N39" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9909</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.0804</v>
+        <v>-0.082</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.077</v>
+        <v>-1.0753</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9909</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9909</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9909</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9909</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9909</v>
       </c>
       <c r="N40" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6054</v>
+        <v>-1.2777</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1328</v>
+        <v>-0.1057</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3628</v>
+        <v>-1.2058</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6054</v>
+        <v>-1.2777</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4339</v>
+        <v>-2.1941</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8285</v>
+        <v>0.9164</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4339</v>
+        <v>-2.1941</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2655</v>
+        <v>-1.1848</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8285</v>
+        <v>0.9164</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>107</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.4370000000000001</v>
+        <v>-0.2684000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>251</v>
@@ -2429,10 +2429,10 @@
         <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4759</v>
+        <v>0.4539</v>
       </c>
       <c r="J2" t="n">
-        <v>11.8975</v>
+        <v>11.3475</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0677</v>
+        <v>-0.0833</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.6925</v>
+        <v>-2.0825</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2177</v>
+        <v>-0.2359</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.4425</v>
+        <v>-5.8975</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.72</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2948</v>
+        <v>-0.3117</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.37</v>
+        <v>-7.7925</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5188</v>
+        <v>-0.5252</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.97</v>
+        <v>-13.13</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1606</v>
+        <v>1.1756</v>
       </c>
       <c r="J7" t="n">
-        <v>29.015</v>
+        <v>29.39</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1116</v>
+        <v>1.1042</v>
       </c>
       <c r="J8" t="n">
-        <v>27.79</v>
+        <v>27.605</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8316</v>
+        <v>0.7922</v>
       </c>
       <c r="J9" t="n">
-        <v>20.79</v>
+        <v>19.805</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5064</v>
+        <v>0.5031</v>
       </c>
       <c r="J10" t="n">
-        <v>12.66</v>
+        <v>12.5775</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.18</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4813</v>
+        <v>0.4805</v>
       </c>
       <c r="J11" t="n">
-        <v>12.0325</v>
+        <v>12.0125</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.99</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1967</v>
+        <v>0.1296</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5406</v>
+        <v>2.3328</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.53</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4287</v>
+        <v>-0.4475</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.7166</v>
+        <v>-8.055</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.49</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4656</v>
+        <v>-0.482</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.380800000000001</v>
+        <v>-8.676</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.47</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4844</v>
+        <v>-0.4996</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.719200000000001</v>
+        <v>-8.992800000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.3</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6489</v>
+        <v>-0.6509</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.6802</v>
+        <v>-11.7162</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.43</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J17" t="n">
-        <v>33.6258</v>
+        <v>33.2154</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.85</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4728</v>
+        <v>1.6109</v>
       </c>
       <c r="J18" t="n">
-        <v>26.5104</v>
+        <v>28.9962</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.65</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2528</v>
+        <v>1.3198</v>
       </c>
       <c r="J19" t="n">
-        <v>22.5504</v>
+        <v>23.7564</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.31</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7323</v>
+        <v>0.715</v>
       </c>
       <c r="J20" t="n">
-        <v>13.1814</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3394</v>
+        <v>-0.3</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.1092</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.43</v>
       </c>
       <c r="I22" t="n">
-        <v>0.769</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>18.456</v>
+        <v>20.4552</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.42</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7562</v>
+        <v>0.8383</v>
       </c>
       <c r="J23" t="n">
-        <v>18.1488</v>
+        <v>20.1192</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5453</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>13.0872</v>
+        <v>14.5536</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.15</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3897</v>
+        <v>0.4261</v>
       </c>
       <c r="J25" t="n">
-        <v>9.3528</v>
+        <v>10.2264</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2926</v>
+        <v>-0.2747</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.0224</v>
+        <v>-6.5928</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2157</v>
+        <v>0.2095</v>
       </c>
       <c r="J27" t="n">
-        <v>5.1768</v>
+        <v>5.028</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.98</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0144</v>
+        <v>-0.026</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3456</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2478</v>
+        <v>-0.2654</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.9472</v>
+        <v>-6.3696</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.73</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2863</v>
+        <v>-0.3032</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.8712</v>
+        <v>-7.2768</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3905</v>
+        <v>-0.4036</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.372</v>
+        <v>-9.686400000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.9</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3054</v>
+        <v>1.4285</v>
       </c>
       <c r="J32" t="n">
-        <v>24.8026</v>
+        <v>27.1415</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.66</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0254</v>
+        <v>1.1328</v>
       </c>
       <c r="J33" t="n">
-        <v>19.4826</v>
+        <v>21.5232</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4606</v>
+        <v>0.5155</v>
       </c>
       <c r="J34" t="n">
-        <v>8.7514</v>
+        <v>9.794499999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2323</v>
+        <v>0.2548</v>
       </c>
       <c r="J35" t="n">
-        <v>4.4137</v>
+        <v>4.8412</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0771</v>
+        <v>0.1083</v>
       </c>
       <c r="J36" t="n">
-        <v>1.4649</v>
+        <v>2.0577</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0519</v>
+        <v>-0.0771</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9861</v>
+        <v>-1.4649</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1014</v>
+        <v>-0.1269</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.9266</v>
+        <v>-2.4111</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.57</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4115</v>
+        <v>-0.4279</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.8185</v>
+        <v>-8.130100000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4208</v>
+        <v>-0.4367</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.9952</v>
+        <v>-8.2973</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.4</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.8509</v>
+        <v>-10.9649</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4623</v>
+        <v>0.5054</v>
       </c>
       <c r="J42" t="n">
-        <v>19.4166</v>
+        <v>21.2268</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.11</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3514</v>
+        <v>0.3586</v>
       </c>
       <c r="J43" t="n">
-        <v>14.7588</v>
+        <v>15.0612</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.08</v>
       </c>
       <c r="I44" t="n">
-        <v>0.278</v>
+        <v>0.2793</v>
       </c>
       <c r="J44" t="n">
-        <v>11.676</v>
+        <v>11.7306</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.05</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1874</v>
+        <v>0.1936</v>
       </c>
       <c r="J45" t="n">
-        <v>7.8708</v>
+        <v>8.1312</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6595</v>
+        <v>-0.6191</v>
       </c>
       <c r="J46" t="n">
-        <v>-27.699</v>
+        <v>-26.0022</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4693</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>19.7106</v>
+        <v>22.0374</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3462</v>
+        <v>0.3619</v>
       </c>
       <c r="J48" t="n">
-        <v>14.5404</v>
+        <v>15.1998</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.13</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2827</v>
+        <v>0.2926</v>
       </c>
       <c r="J49" t="n">
-        <v>11.8734</v>
+        <v>12.2892</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1447</v>
+        <v>0.158</v>
       </c>
       <c r="J50" t="n">
-        <v>6.0774</v>
+        <v>6.636</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1239</v>
+        <v>-0.1331</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.2038</v>
+        <v>-5.5902</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.317</v>
+        <v>0.3207</v>
       </c>
       <c r="J52" t="n">
-        <v>7.925</v>
+        <v>8.0175</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.08</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1651</v>
+        <v>0.1725</v>
       </c>
       <c r="J53" t="n">
-        <v>4.1275</v>
+        <v>4.3125</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.033</v>
+        <v>-0.0405</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.825</v>
+        <v>-1.0125</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1514</v>
+        <v>-0.1656</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.785</v>
+        <v>-4.14</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3597</v>
+        <v>-0.3713</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.9925</v>
+        <v>-9.282500000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.62</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5787</v>
+        <v>0.6632</v>
       </c>
       <c r="J57" t="n">
-        <v>14.4675</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3039</v>
+        <v>0.3214</v>
       </c>
       <c r="J58" t="n">
-        <v>7.5975</v>
+        <v>8.035</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.14</v>
       </c>
       <c r="I59" t="n">
-        <v>0.205</v>
+        <v>0.2236</v>
       </c>
       <c r="J59" t="n">
-        <v>5.125</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.13</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1917</v>
+        <v>0.2103</v>
       </c>
       <c r="J60" t="n">
-        <v>4.7925</v>
+        <v>5.2575</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0716</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.79</v>
+        <v>-1.8725</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.44</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7856</v>
+        <v>0.8694</v>
       </c>
       <c r="J62" t="n">
-        <v>31.424</v>
+        <v>34.776</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.35</v>
       </c>
       <c r="I63" t="n">
-        <v>0.668</v>
+        <v>0.7415</v>
       </c>
       <c r="J63" t="n">
-        <v>26.72</v>
+        <v>29.66</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5337</v>
+        <v>0.5929</v>
       </c>
       <c r="J64" t="n">
-        <v>21.348</v>
+        <v>23.716</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.07</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2096</v>
+        <v>0.225</v>
       </c>
       <c r="J65" t="n">
-        <v>8.384</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0541</v>
+        <v>-0.0374</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.164</v>
+        <v>-1.496</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.23</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4355</v>
+        <v>0.4793</v>
       </c>
       <c r="J67" t="n">
-        <v>17.42</v>
+        <v>19.172</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.018</v>
+        <v>-0.0233</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.72</v>
+        <v>-0.9320000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0964</v>
+        <v>-0.1087</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.856</v>
+        <v>-4.348</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.85</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1838</v>
+        <v>-0.1982</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.352</v>
+        <v>-7.928</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2146</v>
+        <v>-0.2291</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.584</v>
+        <v>-9.164</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.03</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1</v>
+        <v>0.1059</v>
       </c>
       <c r="J72" t="n">
-        <v>4.1</v>
+        <v>4.3419</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0061</v>
+        <v>0.0043</v>
       </c>
       <c r="J73" t="n">
-        <v>0.2501</v>
+        <v>0.1763</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0472</v>
+        <v>-0.0561</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.9352</v>
+        <v>-2.3001</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0843</v>
+        <v>-0.0961</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.4563</v>
+        <v>-3.9401</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1728</v>
+        <v>-0.1873</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.0848</v>
+        <v>-7.6793</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.47</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1112</v>
+        <v>1.0699</v>
       </c>
       <c r="J77" t="n">
-        <v>45.5592</v>
+        <v>43.8659</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.18</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5171</v>
+        <v>0.5051</v>
       </c>
       <c r="J78" t="n">
-        <v>21.2011</v>
+        <v>20.7091</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5171</v>
+        <v>0.5051</v>
       </c>
       <c r="J79" t="n">
-        <v>21.2011</v>
+        <v>20.7091</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2529</v>
+        <v>0.2623</v>
       </c>
       <c r="J80" t="n">
-        <v>10.3689</v>
+        <v>10.7543</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.92</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3358</v>
+        <v>-0.3195</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.7678</v>
+        <v>-13.0995</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2028</v>
+        <v>0.2055</v>
       </c>
       <c r="J82" t="n">
-        <v>5.2728</v>
+        <v>5.343</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1082</v>
+        <v>0.1118</v>
       </c>
       <c r="J83" t="n">
-        <v>2.8132</v>
+        <v>2.9068</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.03</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1082</v>
+        <v>0.1118</v>
       </c>
       <c r="J84" t="n">
-        <v>2.8132</v>
+        <v>2.9068</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1691</v>
+        <v>-0.1845</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.3966</v>
+        <v>-4.797</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.65</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3749</v>
+        <v>-0.3865</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.747400000000001</v>
+        <v>-10.049</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1799</v>
+        <v>1.143</v>
       </c>
       <c r="J87" t="n">
-        <v>30.6774</v>
+        <v>29.718</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7611</v>
+        <v>0.7218</v>
       </c>
       <c r="J88" t="n">
-        <v>19.7886</v>
+        <v>18.7668</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1958</v>
+        <v>0.2078</v>
       </c>
       <c r="J89" t="n">
-        <v>5.0908</v>
+        <v>5.4028</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.02</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0595</v>
+        <v>0.0761</v>
       </c>
       <c r="J90" t="n">
-        <v>1.547</v>
+        <v>1.9786</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4483</v>
+        <v>-0.4237</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.6558</v>
+        <v>-11.0162</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.52</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9878</v>
+        <v>0.9352</v>
       </c>
       <c r="J92" t="n">
-        <v>26.6706</v>
+        <v>25.2504</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1888</v>
+        <v>0.1953</v>
       </c>
       <c r="J93" t="n">
-        <v>5.0976</v>
+        <v>5.2731</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1854</v>
+        <v>-0.1995</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.0058</v>
+        <v>-5.3865</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1958</v>
+        <v>-0.2099</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.2866</v>
+        <v>-5.6673</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.61</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4177</v>
+        <v>-0.4266</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.2779</v>
+        <v>-11.5182</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8809</v>
+        <v>0.8262</v>
       </c>
       <c r="J97" t="n">
-        <v>23.7843</v>
+        <v>22.3074</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5744</v>
       </c>
       <c r="J98" t="n">
-        <v>16.0731</v>
+        <v>15.5088</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.15</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4464</v>
+        <v>0.4399</v>
       </c>
       <c r="J99" t="n">
-        <v>12.0528</v>
+        <v>11.8773</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3428</v>
+        <v>0.3445</v>
       </c>
       <c r="J100" t="n">
-        <v>9.255599999999999</v>
+        <v>9.301500000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.33</v>
+        <v>-0.3154</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.91</v>
+        <v>-8.5158</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5777</v>
+        <v>0.5561</v>
       </c>
       <c r="J102" t="n">
-        <v>14.4425</v>
+        <v>13.9025</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0696</v>
+        <v>-0.0813</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.74</v>
+        <v>-2.0325</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.92</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1043</v>
+        <v>-0.118</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.6075</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1996</v>
+        <v>-0.2152</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.99</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.365</v>
+        <v>-0.3771</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.125</v>
+        <v>-9.4275</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8315</v>
+        <v>0.7836</v>
       </c>
       <c r="J107" t="n">
-        <v>20.7875</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7375</v>
+        <v>0.701</v>
       </c>
       <c r="J108" t="n">
-        <v>18.4375</v>
+        <v>17.525</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5689</v>
+        <v>0.5511</v>
       </c>
       <c r="J109" t="n">
-        <v>14.2225</v>
+        <v>13.7775</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4949</v>
+        <v>0.4844</v>
       </c>
       <c r="J110" t="n">
-        <v>12.3725</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6374</v>
+        <v>-0.594</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.935</v>
+        <v>-14.85</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0239</v>
+        <v>0.9691</v>
       </c>
       <c r="J112" t="n">
-        <v>23.5497</v>
+        <v>22.2893</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="J113" t="n">
-        <v>14.5498</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.19</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>12.3694</v>
+        <v>12.0681</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.07</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2173</v>
+        <v>0.2303</v>
       </c>
       <c r="J115" t="n">
-        <v>4.9979</v>
+        <v>5.2969</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.05</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1548</v>
+        <v>0.1712</v>
       </c>
       <c r="J116" t="n">
-        <v>3.5604</v>
+        <v>3.9376</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.04</v>
       </c>
       <c r="I117" t="n">
-        <v>0.145</v>
+        <v>0.1456</v>
       </c>
       <c r="J117" t="n">
-        <v>3.335</v>
+        <v>3.3488</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.93</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.09</v>
+        <v>-0.1039</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.07</v>
+        <v>-2.3897</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.85</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1752</v>
+        <v>-0.1916</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.0296</v>
+        <v>-4.4068</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1854</v>
+        <v>-0.2019</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.2642</v>
+        <v>-4.6437</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2355</v>
+        <v>-0.2518</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.4165</v>
+        <v>-5.7914</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0168</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>28.4704</v>
+        <v>26.8576</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9211</v>
+        <v>0.8628</v>
       </c>
       <c r="J123" t="n">
-        <v>25.7908</v>
+        <v>24.1584</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6161</v>
+        <v>0.5937</v>
       </c>
       <c r="J124" t="n">
-        <v>17.2508</v>
+        <v>16.6236</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.12</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3669</v>
+        <v>0.3674</v>
       </c>
       <c r="J125" t="n">
-        <v>10.2732</v>
+        <v>10.2872</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9151</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="J126" t="n">
-        <v>-25.6228</v>
+        <v>-23.4696</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5316</v>
+        <v>0.5123</v>
       </c>
       <c r="J127" t="n">
-        <v>14.8848</v>
+        <v>14.3444</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.95</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0674</v>
+        <v>-0.0796</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.8872</v>
+        <v>-2.2288</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0915</v>
+        <v>-0.1051</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.562</v>
+        <v>-2.9428</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.73</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2959</v>
+        <v>-0.3107</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.2852</v>
+        <v>-8.6996</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3437</v>
+        <v>-0.357</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.6236</v>
+        <v>-9.996</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3398</v>
+        <v>0.3383</v>
       </c>
       <c r="J132" t="n">
-        <v>10.194</v>
+        <v>10.149</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.017</v>
+        <v>-0.0226</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.51</v>
+        <v>-0.678</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.92</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1069</v>
+        <v>-0.12</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.207</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.88</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1509</v>
+        <v>-0.1653</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.527</v>
+        <v>-4.959</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.84</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1929</v>
+        <v>-0.2077</v>
       </c>
       <c r="J136" t="n">
-        <v>-5.787</v>
+        <v>-6.231</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.53</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1969</v>
+        <v>1.1605</v>
       </c>
       <c r="J137" t="n">
-        <v>35.907</v>
+        <v>34.815</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.52</v>
       </c>
       <c r="I138" t="n">
-        <v>1.184</v>
+        <v>1.1466</v>
       </c>
       <c r="J138" t="n">
-        <v>35.52</v>
+        <v>34.398</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3284</v>
+        <v>-0.3143</v>
       </c>
       <c r="J139" t="n">
-        <v>-9.852</v>
+        <v>-9.429</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4726</v>
+        <v>-0.4466</v>
       </c>
       <c r="J140" t="n">
-        <v>-14.178</v>
+        <v>-13.398</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.85</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5274</v>
+        <v>-0.4962</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.822</v>
+        <v>-14.886</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.4954</v>
       </c>
       <c r="J142" t="n">
-        <v>17.2924</v>
+        <v>16.8436</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.08</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2157</v>
+        <v>0.2202</v>
       </c>
       <c r="J143" t="n">
-        <v>7.3338</v>
+        <v>7.4868</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.99</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0174</v>
+        <v>-0.0229</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.5916</v>
+        <v>-0.7786</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0959</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.8594</v>
+        <v>-3.2606</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.55</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4704</v>
+        <v>-0.4771</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.9936</v>
+        <v>-16.2214</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.74</v>
+        <v>0.7027</v>
       </c>
       <c r="J147" t="n">
-        <v>25.16</v>
+        <v>23.8918</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.644</v>
+        <v>0.6178</v>
       </c>
       <c r="J148" t="n">
-        <v>21.896</v>
+        <v>21.0052</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6197</v>
+        <v>0.5962</v>
       </c>
       <c r="J149" t="n">
-        <v>21.0698</v>
+        <v>20.2708</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.12</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3697</v>
+        <v>0.3693</v>
       </c>
       <c r="J150" t="n">
-        <v>12.5698</v>
+        <v>12.5562</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4462</v>
+        <v>-0.4223</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.1708</v>
+        <v>-14.3582</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.91</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0487</v>
+        <v>-0.0774</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.974</v>
+        <v>-1.548</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.7</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2848</v>
+        <v>-0.3078</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.696</v>
+        <v>-6.156</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.61</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3679</v>
+        <v>-0.3877</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.358</v>
+        <v>-7.754</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4695</v>
+        <v>-0.4836</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.672000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.4</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5642</v>
+        <v>-0.5716</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.284</v>
+        <v>-11.432</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.89</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5466</v>
+        <v>1.5451</v>
       </c>
       <c r="J157" t="n">
-        <v>30.932</v>
+        <v>30.902</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.63</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2486</v>
+        <v>1.2291</v>
       </c>
       <c r="J158" t="n">
-        <v>24.972</v>
+        <v>24.582</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.53</v>
       </c>
       <c r="I159" t="n">
-        <v>1.1314</v>
+        <v>1.103</v>
       </c>
       <c r="J159" t="n">
-        <v>22.628</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.36</v>
       </c>
       <c r="I160" t="n">
-        <v>0.8754</v>
+        <v>0.8348</v>
       </c>
       <c r="J160" t="n">
-        <v>17.508</v>
+        <v>16.696</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.342</v>
+        <v>-0.3095</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.84</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.92</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0381</v>
+        <v>-0.0663</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.8763</v>
+        <v>-1.5249</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.71</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2762</v>
+        <v>-0.2993</v>
       </c>
       <c r="J163" t="n">
-        <v>-6.3526</v>
+        <v>-6.8839</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.63</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3513</v>
+        <v>-0.3716</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.0799</v>
+        <v>-8.546799999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.53</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4424</v>
+        <v>-0.4581</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.1752</v>
+        <v>-10.5363</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.36</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.6075</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.8759</v>
+        <v>-13.9725</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.84</v>
       </c>
       <c r="I167" t="n">
-        <v>1.4853</v>
+        <v>1.4814</v>
       </c>
       <c r="J167" t="n">
-        <v>34.1619</v>
+        <v>34.0722</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.71</v>
       </c>
       <c r="I168" t="n">
-        <v>1.3374</v>
+        <v>1.3247</v>
       </c>
       <c r="J168" t="n">
-        <v>30.7602</v>
+        <v>30.4681</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.827</v>
+        <v>0.7932</v>
       </c>
       <c r="J169" t="n">
-        <v>19.021</v>
+        <v>18.2436</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.29</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7145</v>
+        <v>0.6942</v>
       </c>
       <c r="J170" t="n">
-        <v>16.4335</v>
+        <v>15.9666</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.29</v>
       </c>
       <c r="I171" t="n">
-        <v>0.7145</v>
+        <v>0.6942</v>
       </c>
       <c r="J171" t="n">
-        <v>16.4335</v>
+        <v>15.9666</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.2</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3649</v>
+        <v>0.3617</v>
       </c>
       <c r="J172" t="n">
-        <v>9.1225</v>
+        <v>9.0425</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.02</v>
       </c>
       <c r="I173" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0708</v>
       </c>
       <c r="J173" t="n">
-        <v>1.715</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2269</v>
+        <v>-0.243</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.6725</v>
+        <v>-6.075</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.75</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2761</v>
+        <v>-0.2914</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.9025</v>
+        <v>-7.285</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2954</v>
+        <v>-0.3103</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.385</v>
+        <v>-7.7575</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.39</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5013</v>
+        <v>0.5105</v>
       </c>
       <c r="J177" t="n">
-        <v>12.5325</v>
+        <v>12.7625</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5013</v>
+        <v>0.5105</v>
       </c>
       <c r="J178" t="n">
-        <v>12.5325</v>
+        <v>12.7625</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1376</v>
+        <v>0.1555</v>
       </c>
       <c r="J179" t="n">
-        <v>3.44</v>
+        <v>3.8875</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.08</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1229</v>
+        <v>0.1406</v>
       </c>
       <c r="J180" t="n">
-        <v>3.0725</v>
+        <v>3.515</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.06</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0924</v>
+        <v>0.1094</v>
       </c>
       <c r="J181" t="n">
-        <v>2.31</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3876</v>
+        <v>1.371</v>
       </c>
       <c r="J182" t="n">
-        <v>36.0776</v>
+        <v>35.646</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0693</v>
+        <v>1.0281</v>
       </c>
       <c r="J183" t="n">
-        <v>27.8018</v>
+        <v>26.7306</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.41</v>
       </c>
       <c r="I184" t="n">
-        <v>0.9981</v>
+        <v>0.9462</v>
       </c>
       <c r="J184" t="n">
-        <v>25.9506</v>
+        <v>24.6012</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.01</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0188</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.4888</v>
+        <v>0.2262</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3691</v>
+        <v>-0.3429</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.5966</v>
+        <v>-8.9154</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.88</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1309</v>
+        <v>-0.15</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.4034</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.82</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1945</v>
+        <v>-0.2136</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.057</v>
+        <v>-5.5536</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2237</v>
+        <v>-0.2427</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.8162</v>
+        <v>-6.3102</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2893</v>
+        <v>-0.3074</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.5218</v>
+        <v>-7.9924</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.71</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2988</v>
+        <v>-0.3166</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.7688</v>
+        <v>-8.2316</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.698</v>
+        <v>0.66</v>
       </c>
       <c r="J192" t="n">
-        <v>18.846</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.16</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4939</v>
+        <v>0.4781</v>
       </c>
       <c r="J193" t="n">
-        <v>13.3353</v>
+        <v>12.9087</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3313</v>
+        <v>0.3298</v>
       </c>
       <c r="J194" t="n">
-        <v>8.9451</v>
+        <v>8.9046</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.06</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2155</v>
+        <v>0.2212</v>
       </c>
       <c r="J195" t="n">
-        <v>5.8185</v>
+        <v>5.9724</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.73</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.7559</v>
       </c>
       <c r="J196" t="n">
-        <v>-22.032</v>
+        <v>-20.4093</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8079</v>
+        <v>0.7739</v>
       </c>
       <c r="J197" t="n">
-        <v>21.8133</v>
+        <v>20.8953</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.32</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6262</v>
+        <v>0.61</v>
       </c>
       <c r="J198" t="n">
-        <v>16.9074</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.91</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1309</v>
+        <v>-0.1415</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.5343</v>
+        <v>-3.8205</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1309</v>
+        <v>-0.1415</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.5343</v>
+        <v>-3.8205</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.79</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.257</v>
+        <v>-0.2686</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.939</v>
+        <v>-7.2522</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5429</v>
+        <v>0.5239</v>
       </c>
       <c r="J202" t="n">
-        <v>14.1154</v>
+        <v>13.6214</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.02</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0838</v>
+        <v>0.0861</v>
       </c>
       <c r="J203" t="n">
-        <v>2.1788</v>
+        <v>2.2386</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0814</v>
+        <v>-0.0939</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.1164</v>
+        <v>-2.4414</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.83</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1991</v>
+        <v>-0.2148</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.1766</v>
+        <v>-5.5848</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.448</v>
+        <v>-0.4565</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.648</v>
+        <v>-11.869</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.41</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0141</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="J207" t="n">
-        <v>26.3666</v>
+        <v>24.9652</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.7875</v>
       </c>
       <c r="J208" t="n">
-        <v>21.6086</v>
+        <v>20.475</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.763</v>
+        <v>0.7275</v>
       </c>
       <c r="J209" t="n">
-        <v>19.838</v>
+        <v>18.915</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.24</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6486</v>
+        <v>0.6258</v>
       </c>
       <c r="J210" t="n">
-        <v>16.8636</v>
+        <v>16.2708</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.89</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4396</v>
+        <v>-0.4116</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.4296</v>
+        <v>-10.7016</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4076</v>
+        <v>0.3999</v>
       </c>
       <c r="J212" t="n">
-        <v>11.4128</v>
+        <v>11.1972</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1082</v>
+        <v>0.1118</v>
       </c>
       <c r="J213" t="n">
-        <v>3.0296</v>
+        <v>3.1304</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1046</v>
+        <v>-0.1182</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.9288</v>
+        <v>-3.3096</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1795</v>
+        <v>-0.1949</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.026</v>
+        <v>-5.4572</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.67</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3561</v>
+        <v>-0.3684</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.970800000000001</v>
+        <v>-10.3152</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.45</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0812</v>
+        <v>1.0367</v>
       </c>
       <c r="J217" t="n">
-        <v>30.2736</v>
+        <v>29.0276</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.29</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7755</v>
+        <v>0.7361</v>
       </c>
       <c r="J218" t="n">
-        <v>21.714</v>
+        <v>20.6108</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.14</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4149</v>
+        <v>0.4125</v>
       </c>
       <c r="J219" t="n">
-        <v>11.6172</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0519</v>
+        <v>0.0708</v>
       </c>
       <c r="J220" t="n">
-        <v>1.4532</v>
+        <v>1.9824</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.01</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0108</v>
+        <v>0.0294</v>
       </c>
       <c r="J221" t="n">
-        <v>0.3024</v>
+        <v>0.8232</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.21</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6148</v>
+        <v>0.5879</v>
       </c>
       <c r="J222" t="n">
-        <v>17.2144</v>
+        <v>16.4612</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.487</v>
+        <v>0.4734</v>
       </c>
       <c r="J223" t="n">
-        <v>13.636</v>
+        <v>13.2552</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.16</v>
       </c>
       <c r="I224" t="n">
-        <v>0.487</v>
+        <v>0.4734</v>
       </c>
       <c r="J224" t="n">
-        <v>13.636</v>
+        <v>13.2552</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0369</v>
+        <v>0.0475</v>
       </c>
       <c r="J225" t="n">
-        <v>1.0332</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.86</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4844</v>
+        <v>-0.4605</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.5632</v>
+        <v>-12.894</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.29</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5967</v>
+        <v>0.5793</v>
       </c>
       <c r="J227" t="n">
-        <v>16.7076</v>
+        <v>16.2204</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.19</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4178</v>
+        <v>0.4148</v>
       </c>
       <c r="J228" t="n">
-        <v>11.6984</v>
+        <v>11.6144</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2444</v>
+        <v>0.2511</v>
       </c>
       <c r="J229" t="n">
-        <v>6.8432</v>
+        <v>7.0308</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1009</v>
+        <v>-0.1122</v>
       </c>
       <c r="J230" t="n">
-        <v>-2.8252</v>
+        <v>-3.1416</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4933</v>
+        <v>-0.4981</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.8124</v>
+        <v>-13.9468</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.51</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1504</v>
+        <v>1.1145</v>
       </c>
       <c r="J232" t="n">
-        <v>29.9104</v>
+        <v>28.977</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.5</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1376</v>
+        <v>1.1009</v>
       </c>
       <c r="J233" t="n">
-        <v>29.5776</v>
+        <v>28.6234</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2702</v>
+        <v>0.2812</v>
       </c>
       <c r="J234" t="n">
-        <v>7.0252</v>
+        <v>7.3112</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1076</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.7976</v>
+        <v>-2.5012</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.99</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1076</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J236" t="n">
-        <v>-2.7976</v>
+        <v>-2.5012</v>
       </c>
     </row>
     <row r="237">
@@ -11869,10 +11869,10 @@
         <v>0.92</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1011</v>
+        <v>-0.1156</v>
       </c>
       <c r="J238" t="n">
-        <v>-2.6286</v>
+        <v>-3.0056</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1233</v>
+        <v>-0.1386</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.2058</v>
+        <v>-3.6036</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2051</v>
+        <v>-0.2217</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.3326</v>
+        <v>-5.7642</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.74</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2839</v>
+        <v>-0.2994</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.3814</v>
+        <v>-7.7844</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3833/event_3833_evp_summary.xlsx
+++ b/database/event/3833/event_3833_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6886</v>
+        <v>6.8961</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5532</v>
+        <v>0.5704</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4206</v>
+        <v>2.5357</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6886</v>
+        <v>6.8961</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3713</v>
+        <v>2.4554</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3173</v>
+        <v>4.4407</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9297</v>
+        <v>2.7761</v>
       </c>
       <c r="I2" t="n">
-        <v>1.582</v>
+        <v>1.5587</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3173</v>
+        <v>4.4407</v>
       </c>
       <c r="K2" t="n">
         <v>104</v>
@@ -529,7 +529,7 @@
         <v>86</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8993</v>
+        <v>5.9994</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9925</v>
+        <v>5.9061</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4957</v>
+        <v>0.4885</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1037</v>
+        <v>2.0847</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9925</v>
+        <v>5.9061</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7348</v>
+        <v>1.6555</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2577</v>
+        <v>4.2506</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7348</v>
+        <v>1.6555</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9368</v>
+        <v>0.9295</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2577</v>
+        <v>4.2506</v>
       </c>
       <c r="K3" t="n">
         <v>104</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1945</v>
+        <v>5.1801</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2109</v>
+        <v>5.1543</v>
       </c>
       <c r="C4" t="n">
-        <v>0.431</v>
+        <v>0.4263</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7479</v>
+        <v>1.7422</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2109</v>
+        <v>5.1543</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1573</v>
+        <v>3.1164</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0536</v>
+        <v>2.0379</v>
       </c>
       <c r="H4" t="n">
-        <v>5.523</v>
+        <v>5.2578</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9824</v>
+        <v>2.9521</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0536</v>
+        <v>2.0379</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>5.036</v>
+        <v>4.99</v>
       </c>
       <c r="N4" t="n">
         <v>190</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5899</v>
+        <v>4.448</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3797</v>
+        <v>0.3679</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4652</v>
+        <v>1.4205</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5899</v>
+        <v>4.448</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1486</v>
+        <v>3.1182</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4413</v>
+        <v>1.3298</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4942</v>
+        <v>5.2646</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9668</v>
+        <v>2.9559</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4413</v>
+        <v>1.3298</v>
       </c>
       <c r="K5" t="n">
         <v>69</v>
@@ -667,7 +667,7 @@
         <v>150</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4081</v>
+        <v>4.2857</v>
       </c>
       <c r="N5" t="n">
         <v>219</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8846</v>
+        <v>3.7621</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3213</v>
+        <v>0.3112</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1441</v>
+        <v>1.108</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8846</v>
+        <v>3.7621</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1596</v>
+        <v>2.0275</v>
       </c>
       <c r="G6" t="n">
-        <v>0.725</v>
+        <v>1.7346</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5306</v>
+        <v>2.0275</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9865</v>
+        <v>1.1384</v>
       </c>
       <c r="J6" t="n">
-        <v>0.725</v>
+        <v>1.7346</v>
       </c>
       <c r="K6" t="n">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="L6" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7115</v>
+        <v>2.873</v>
       </c>
       <c r="N6" t="n">
-        <v>251</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7899</v>
+        <v>3.7178</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3135</v>
+        <v>0.3075</v>
       </c>
       <c r="D7" t="n">
-        <v>1.101</v>
+        <v>1.0878</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7899</v>
+        <v>3.7178</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6966</v>
+        <v>3.0607</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0933</v>
+        <v>0.6571</v>
       </c>
       <c r="H7" t="n">
-        <v>4.0028</v>
+        <v>5.0487</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1615</v>
+        <v>2.8347</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0933</v>
+        <v>0.6571</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>107</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2548</v>
+        <v>3.4918</v>
       </c>
       <c r="N7" t="n">
         <v>251</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7881</v>
+        <v>3.6371</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3133</v>
+        <v>0.3008</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1002</v>
+        <v>1.0511</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7881</v>
+        <v>3.6371</v>
       </c>
       <c r="F8" t="n">
+        <v>2.6891</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.6535</v>
+      </c>
+      <c r="I8" t="n">
         <v>2.0513</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.7368</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.0513</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.1077</v>
-      </c>
       <c r="J8" t="n">
-        <v>1.7368</v>
+        <v>0.948</v>
       </c>
       <c r="K8" t="n">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="L8" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8445</v>
+        <v>2.9993</v>
       </c>
       <c r="N8" t="n">
-        <v>190</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6403</v>
+        <v>3.5374</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3011</v>
+        <v>0.2926</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0329</v>
+        <v>1.0057</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6403</v>
+        <v>3.5374</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4729</v>
+        <v>3.4156</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1674</v>
+        <v>0.1218</v>
       </c>
       <c r="H9" t="n">
-        <v>6.5642</v>
+        <v>6.3809</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5446</v>
+        <v>3.5827</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1674</v>
+        <v>0.1218</v>
       </c>
       <c r="K9" t="n">
         <v>69</v>
@@ -851,7 +851,7 @@
         <v>150</v>
       </c>
       <c r="M9" t="n">
-        <v>3.712</v>
+        <v>3.7045</v>
       </c>
       <c r="N9" t="n">
         <v>219</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3559</v>
+        <v>3.2926</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2776</v>
+        <v>0.2723</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9035</v>
+        <v>0.8941</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3559</v>
+        <v>3.2926</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6984</v>
+        <v>3.599</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3425</v>
+        <v>-0.3064</v>
       </c>
       <c r="H10" t="n">
-        <v>7.3081</v>
+        <v>7.0697</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9463</v>
+        <v>3.9694</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3425</v>
+        <v>-0.3064</v>
       </c>
       <c r="K10" t="n">
         <v>146</v>
@@ -897,7 +897,7 @@
         <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6038</v>
+        <v>3.663</v>
       </c>
       <c r="N10" t="n">
         <v>189</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3113</v>
+        <v>3.1798</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2739</v>
+        <v>0.263</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8832</v>
+        <v>0.8428</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3113</v>
+        <v>3.1798</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4323</v>
+        <v>3.3028</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.121</v>
+        <v>-0.123</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4303</v>
+        <v>5.9574</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4723</v>
+        <v>3.3449</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.121</v>
+        <v>-0.123</v>
       </c>
       <c r="K11" t="n">
         <v>144</v>
@@ -943,7 +943,7 @@
         <v>107</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3513</v>
+        <v>3.2219</v>
       </c>
       <c r="N11" t="n">
         <v>251</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2205</v>
+        <v>3.1715</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2664</v>
+        <v>0.2623</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8418</v>
+        <v>0.839</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2205</v>
+        <v>3.1715</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3588</v>
+        <v>3.3091</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1383</v>
+        <v>-0.1376</v>
       </c>
       <c r="H12" t="n">
-        <v>6.1877</v>
+        <v>5.9813</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3413</v>
+        <v>3.3583</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1383</v>
+        <v>-0.1376</v>
       </c>
       <c r="K12" t="n">
         <v>69</v>
@@ -989,7 +989,7 @@
         <v>150</v>
       </c>
       <c r="M12" t="n">
-        <v>3.203</v>
+        <v>3.2207</v>
       </c>
       <c r="N12" t="n">
         <v>219</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2707</v>
+        <v>2.2677</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1878</v>
+        <v>0.1876</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4095</v>
+        <v>0.4273</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2707</v>
+        <v>2.2677</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7334</v>
+        <v>2.7153</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4627</v>
+        <v>-0.4476</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1243</v>
+        <v>3.7518</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2271</v>
+        <v>2.1065</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4627</v>
+        <v>-0.4476</v>
       </c>
       <c r="K13" t="n">
         <v>146</v>
@@ -1035,7 +1035,7 @@
         <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7644</v>
+        <v>1.6589</v>
       </c>
       <c r="N13" t="n">
         <v>189</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1143</v>
+        <v>1.9685</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1749</v>
+        <v>0.1628</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3383</v>
+        <v>0.291</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1143</v>
+        <v>1.9685</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0547</v>
+        <v>1.9552</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0596</v>
+        <v>0.0133</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0547</v>
+        <v>1.9552</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1095</v>
+        <v>1.0978</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0596</v>
+        <v>0.0133</v>
       </c>
       <c r="K14" t="n">
         <v>69</v>
@@ -1081,7 +1081,7 @@
         <v>150</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1691</v>
+        <v>1.1111</v>
       </c>
       <c r="N14" t="n">
         <v>219</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3387</v>
+        <v>1.4091</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1107</v>
+        <v>0.1166</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0148</v>
+        <v>0.0361</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3387</v>
+        <v>1.4091</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4308</v>
+        <v>-1.332</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7695</v>
+        <v>2.7411</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4308</v>
+        <v>-1.332</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7726</v>
+        <v>-0.7479</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7695</v>
+        <v>2.7411</v>
       </c>
       <c r="K15" t="n">
         <v>104</v>
@@ -1127,7 +1127,7 @@
         <v>86</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9969</v>
+        <v>1.9932</v>
       </c>
       <c r="N15" t="n">
         <v>190</v>
@@ -1136,185 +1136,185 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1941</v>
+        <v>1.1416</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0988</v>
+        <v>0.0944</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0806</v>
+        <v>-0.0857</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1941</v>
+        <v>1.1416</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1941</v>
+        <v>2.011</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.8694</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1941</v>
+        <v>2.011</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1941</v>
+        <v>1.1291</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.8694</v>
       </c>
       <c r="K16" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1941</v>
+        <v>0.2597</v>
       </c>
       <c r="N16" t="n">
-        <v>158</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1225</v>
+        <v>1.0335</v>
       </c>
       <c r="C17" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1132</v>
+        <v>-0.135</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1225</v>
+        <v>1.0335</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1032</v>
+        <v>1.0335</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9807</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1032</v>
+        <v>1.0335</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1357</v>
+        <v>1.0335</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9807</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1549999999999999</v>
+        <v>1.0335</v>
       </c>
       <c r="N17" t="n">
-        <v>189</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1156</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1164</v>
+        <v>-0.1592</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1156</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0693</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9537</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0693</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1174</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9537</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="L18" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1637</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0493</v>
+        <v>0.8761</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0868</v>
+        <v>0.0725</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1465</v>
+        <v>-0.2067</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0493</v>
+        <v>0.8761</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0493</v>
+        <v>1.8542</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.9781</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0493</v>
+        <v>1.8542</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0493</v>
+        <v>1.0411</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.9781</v>
       </c>
       <c r="K19" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0493</v>
+        <v>0.06299999999999994</v>
       </c>
       <c r="N19" t="n">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9666</v>
+        <v>0.7761</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1842</v>
+        <v>-0.2522</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9666</v>
+        <v>0.7761</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3967</v>
+        <v>1.1714</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4301</v>
+        <v>-0.3953</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3967</v>
+        <v>1.1714</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7542</v>
+        <v>0.6577</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4301</v>
+        <v>-0.3953</v>
       </c>
       <c r="K20" t="n">
         <v>146</v>
@@ -1357,7 +1357,7 @@
         <v>43</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3241</v>
+        <v>0.2624</v>
       </c>
       <c r="N20" t="n">
         <v>189</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8738</v>
+        <v>0.7533</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0723</v>
+        <v>0.0623</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2264</v>
+        <v>-0.2626</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8738</v>
+        <v>0.7533</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8738</v>
+        <v>0.7533</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8738</v>
+        <v>0.7533</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8738</v>
+        <v>0.7533</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8738</v>
+        <v>0.7533</v>
       </c>
       <c r="N21" t="n">
         <v>158</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2169</v>
+        <v>0.1917</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0179</v>
+        <v>0.0159</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5255</v>
+        <v>-0.5185</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2169</v>
+        <v>0.1917</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2169</v>
+        <v>0.1917</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2169</v>
+        <v>0.1917</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2169</v>
+        <v>0.1917</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2169</v>
+        <v>0.1917</v>
       </c>
       <c r="N22" t="n">
         <v>77</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1768</v>
+        <v>0.1449</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0146</v>
+        <v>0.012</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5437</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1768</v>
+        <v>0.1449</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1768</v>
+        <v>0.1449</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1768</v>
+        <v>0.1449</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1768</v>
+        <v>0.1449</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1768</v>
+        <v>0.1449</v>
       </c>
       <c r="N23" t="n">
         <v>90</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1461</v>
+        <v>0.1226</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0121</v>
+        <v>0.0101</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5577</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1461</v>
+        <v>0.1226</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1461</v>
+        <v>0.1226</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1461</v>
+        <v>0.1226</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1461</v>
+        <v>0.1226</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1461</v>
+        <v>0.1226</v>
       </c>
       <c r="N24" t="n">
         <v>138</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1059</v>
+        <v>0.0873</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0072</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.576</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1059</v>
+        <v>0.0873</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1059</v>
+        <v>0.0873</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1059</v>
+        <v>0.0873</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1059</v>
+        <v>0.0873</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1059</v>
+        <v>0.0873</v>
       </c>
       <c r="N25" t="n">
         <v>77</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>QKA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.08</v>
+        <v>0.0356</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0066</v>
+        <v>0.0029</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5878</v>
+        <v>-0.5896</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08</v>
+        <v>0.0356</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08</v>
+        <v>0.0356</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08</v>
+        <v>0.0356</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08</v>
+        <v>0.0356</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.08</v>
+        <v>0.0356</v>
       </c>
       <c r="N26" t="n">
-        <v>158</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QKA</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0522</v>
+        <v>0.015</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0043</v>
+        <v>0.0012</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6004</v>
+        <v>-0.599</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0522</v>
+        <v>0.015</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0522</v>
+        <v>0.015</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0522</v>
+        <v>0.015</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0522</v>
+        <v>0.015</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0522</v>
+        <v>0.015</v>
       </c>
       <c r="N27" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0307</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6102</v>
+        <v>-0.602</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0307</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0307</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0307</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0307</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0307</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="N28" t="n">
         <v>90</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0785</v>
+        <v>-0.1223</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0065</v>
+        <v>-0.0101</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6599</v>
+        <v>-0.6615</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0785</v>
+        <v>-0.1223</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0785</v>
+        <v>-0.1223</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0785</v>
+        <v>-0.1223</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0785</v>
+        <v>-0.1223</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0785</v>
+        <v>-0.1223</v>
       </c>
       <c r="N29" t="n">
         <v>138</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2092</v>
+        <v>-0.213</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0173</v>
+        <v>-0.0176</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7194</v>
+        <v>-0.7028</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2092</v>
+        <v>-0.213</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2092</v>
+        <v>-0.213</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2092</v>
+        <v>-0.213</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2092</v>
+        <v>-0.213</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2092</v>
+        <v>-0.213</v>
       </c>
       <c r="N30" t="n">
         <v>90</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2453</v>
+        <v>-0.2376</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0203</v>
+        <v>-0.0197</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7359</v>
+        <v>-0.714</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2453</v>
+        <v>-0.2376</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2453</v>
+        <v>-0.2376</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2453</v>
+        <v>-0.2376</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2453</v>
+        <v>-0.2376</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2453</v>
+        <v>-0.2376</v>
       </c>
       <c r="N31" t="n">
         <v>77</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>ImpressioN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2832</v>
+        <v>-0.2519</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0234</v>
+        <v>-0.0208</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7531</v>
+        <v>-0.7205</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2832</v>
+        <v>-0.2519</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0648</v>
+        <v>-0.2519</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2184</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0648</v>
+        <v>-0.2519</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.035</v>
+        <v>-0.2519</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2184</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="L32" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2534</v>
+        <v>-0.2519</v>
       </c>
       <c r="N32" t="n">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ImpressioN</t>
+          <t>morelz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2867</v>
+        <v>-0.2889</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0237</v>
+        <v>-0.0239</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7547</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2867</v>
+        <v>-0.2889</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2867</v>
+        <v>-0.1455</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.1434</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2867</v>
+        <v>-0.1455</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2867</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.1434</v>
       </c>
       <c r="K33" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2867</v>
+        <v>-0.2251</v>
       </c>
       <c r="N33" t="n">
-        <v>138</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>morelz</t>
+          <t>splashske</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3149</v>
+        <v>-0.3316</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.026</v>
+        <v>-0.0274</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.7568</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3149</v>
+        <v>-0.3316</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1689</v>
+        <v>-0.3316</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.146</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1689</v>
+        <v>-0.3316</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0912</v>
+        <v>-0.3316</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.146</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L34" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2372</v>
+        <v>-0.3316</v>
       </c>
       <c r="N34" t="n">
-        <v>251</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>splashske</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3275</v>
+        <v>-0.382</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0271</v>
+        <v>-0.0316</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7733</v>
+        <v>-0.7798</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3275</v>
+        <v>-0.382</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3275</v>
+        <v>-0.1325</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.2495</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3275</v>
+        <v>-0.1325</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3275</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.2495</v>
       </c>
       <c r="K35" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3275</v>
+        <v>-0.3239</v>
       </c>
       <c r="N35" t="n">
-        <v>138</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5085</v>
+        <v>-0.4613</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0421</v>
+        <v>-0.0382</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8557</v>
+        <v>-0.8159</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5085</v>
+        <v>-0.4613</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5085</v>
+        <v>-0.4613</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5085</v>
+        <v>-0.4613</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5085</v>
+        <v>-0.4613</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5085</v>
+        <v>-0.4613</v>
       </c>
       <c r="N36" t="n">
         <v>77</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>malta</t>
+          <t>shuadapai</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6679</v>
+        <v>-0.6776</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0552</v>
+        <v>-0.056</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9282</v>
+        <v>-0.9145</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6679</v>
+        <v>-0.6776</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6679</v>
+        <v>-0.6776</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6679</v>
+        <v>-0.6776</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6679</v>
+        <v>-0.6776</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6679</v>
+        <v>-0.6776</v>
       </c>
       <c r="N37" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>shuadapai</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7127</v>
+        <v>-0.6823</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.059</v>
+        <v>-0.0564</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9486</v>
+        <v>-0.9166</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7127</v>
+        <v>-0.6823</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7127</v>
+        <v>-0.6823</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7127</v>
+        <v>-0.6823</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7127</v>
+        <v>-0.6823</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7127</v>
+        <v>-0.6823</v>
       </c>
       <c r="N38" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.988</v>
+        <v>-0.906</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.074</v>
+        <v>-1.0185</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.988</v>
+        <v>-0.906</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.988</v>
+        <v>-0.906</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.988</v>
+        <v>-0.906</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.988</v>
+        <v>-0.906</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.988</v>
+        <v>-0.906</v>
       </c>
       <c r="N39" t="n">
         <v>158</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9909</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.082</v>
+        <v>-0.0827</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0753</v>
+        <v>-1.0611</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9909</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9909</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9909</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9909</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9909</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>138</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2777</v>
+        <v>-1.0928</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1057</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2058</v>
+        <v>-1.1036</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2777</v>
+        <v>-1.0928</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.1941</v>
+        <v>-1.9314</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9164</v>
+        <v>0.8386</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.1941</v>
+        <v>-1.9314</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1848</v>
+        <v>-1.0844</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9164</v>
+        <v>0.8386</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>107</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.2684000000000001</v>
+        <v>-0.2458</v>
       </c>
       <c r="N41" t="n">
         <v>251</v>
@@ -2429,10 +2429,10 @@
         <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4539</v>
+        <v>0.4033</v>
       </c>
       <c r="J2" t="n">
-        <v>11.3475</v>
+        <v>10.0825</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0833</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.0825</v>
+        <v>-1.7625</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2359</v>
+        <v>-0.2177</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.8975</v>
+        <v>-5.4425</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.72</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3117</v>
+        <v>-0.2946</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.7925</v>
+        <v>-7.365</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5252</v>
+        <v>-0.5281</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.13</v>
+        <v>-13.2025</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1756</v>
+        <v>1.1894</v>
       </c>
       <c r="J7" t="n">
-        <v>29.39</v>
+        <v>29.735</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1042</v>
+        <v>1.1105</v>
       </c>
       <c r="J8" t="n">
-        <v>27.605</v>
+        <v>27.7625</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7922</v>
+        <v>0.7745</v>
       </c>
       <c r="J9" t="n">
-        <v>19.805</v>
+        <v>19.3625</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5031</v>
+        <v>0.4734</v>
       </c>
       <c r="J10" t="n">
-        <v>12.5775</v>
+        <v>11.835</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.18</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4805</v>
+        <v>0.4503</v>
       </c>
       <c r="J11" t="n">
-        <v>12.0125</v>
+        <v>11.2575</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.99</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1296</v>
+        <v>0.1726</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3328</v>
+        <v>3.1068</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.53</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4475</v>
+        <v>-0.443</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.055</v>
+        <v>-7.974</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.49</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.482</v>
+        <v>-0.4794</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.676</v>
+        <v>-8.629200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.47</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4996</v>
+        <v>-0.4983</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.992800000000001</v>
+        <v>-8.9694</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.3</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6509</v>
+        <v>-0.6704</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.7162</v>
+        <v>-12.0672</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.43</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J17" t="n">
-        <v>33.2154</v>
+        <v>35.6796</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.85</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6109</v>
+        <v>1.6409</v>
       </c>
       <c r="J18" t="n">
-        <v>28.9962</v>
+        <v>29.5362</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.65</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3198</v>
+        <v>1.3611</v>
       </c>
       <c r="J19" t="n">
-        <v>23.7564</v>
+        <v>24.4998</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.31</v>
       </c>
       <c r="I20" t="n">
-        <v>0.715</v>
+        <v>0.6988</v>
       </c>
       <c r="J20" t="n">
-        <v>12.87</v>
+        <v>12.5784</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3</v>
+        <v>-0.2757</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.4</v>
+        <v>-4.9626</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.43</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8373</v>
       </c>
       <c r="J22" t="n">
-        <v>20.4552</v>
+        <v>20.0952</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.42</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8383</v>
+        <v>0.8233</v>
       </c>
       <c r="J23" t="n">
-        <v>20.1192</v>
+        <v>19.7592</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.5976</v>
       </c>
       <c r="J24" t="n">
-        <v>14.5536</v>
+        <v>14.3424</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.15</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4261</v>
+        <v>0.3945</v>
       </c>
       <c r="J25" t="n">
-        <v>10.2264</v>
+        <v>9.468</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2747</v>
+        <v>-0.2372</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.5928</v>
+        <v>-5.6928</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2095</v>
+        <v>0.1699</v>
       </c>
       <c r="J27" t="n">
-        <v>5.028</v>
+        <v>4.0776</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.98</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.026</v>
+        <v>-0.0188</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.624</v>
+        <v>-0.4512</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2654</v>
+        <v>-0.2471</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.3696</v>
+        <v>-5.9304</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.73</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3032</v>
+        <v>-0.2858</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.2768</v>
+        <v>-6.8592</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4036</v>
+        <v>-0.3925</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.686400000000001</v>
+        <v>-9.42</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.9</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4285</v>
+        <v>1.4407</v>
       </c>
       <c r="J32" t="n">
-        <v>27.1415</v>
+        <v>27.3733</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.66</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1328</v>
+        <v>1.126</v>
       </c>
       <c r="J33" t="n">
-        <v>21.5232</v>
+        <v>21.394</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5155</v>
+        <v>0.5107</v>
       </c>
       <c r="J34" t="n">
-        <v>9.794499999999999</v>
+        <v>9.7033</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2548</v>
+        <v>0.2233</v>
       </c>
       <c r="J35" t="n">
-        <v>4.8412</v>
+        <v>4.2427</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1083</v>
+        <v>0.0833</v>
       </c>
       <c r="J36" t="n">
-        <v>2.0577</v>
+        <v>1.5827</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.92</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0771</v>
+        <v>-0.0593</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.4649</v>
+        <v>-1.1267</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1269</v>
+        <v>-0.1095</v>
       </c>
       <c r="J38" t="n">
-        <v>-2.4111</v>
+        <v>-2.0805</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.57</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4279</v>
+        <v>-0.4194</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.130100000000001</v>
+        <v>-7.9686</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4367</v>
+        <v>-0.4288</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.2973</v>
+        <v>-8.1472</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.4</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.5856</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.9649</v>
+        <v>-11.1264</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5054</v>
+        <v>0.487</v>
       </c>
       <c r="J42" t="n">
-        <v>21.2268</v>
+        <v>20.454</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.11</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3586</v>
+        <v>0.3176</v>
       </c>
       <c r="J43" t="n">
-        <v>15.0612</v>
+        <v>13.3392</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.08</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2793</v>
+        <v>0.2413</v>
       </c>
       <c r="J44" t="n">
-        <v>11.7306</v>
+        <v>10.1346</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.05</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1936</v>
+        <v>0.1616</v>
       </c>
       <c r="J45" t="n">
-        <v>8.1312</v>
+        <v>6.7872</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6191</v>
+        <v>-0.5816</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.0022</v>
+        <v>-24.4272</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.494</v>
       </c>
       <c r="J47" t="n">
-        <v>22.0374</v>
+        <v>20.748</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3619</v>
+        <v>0.3096</v>
       </c>
       <c r="J48" t="n">
-        <v>15.1998</v>
+        <v>13.0032</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.13</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2926</v>
+        <v>0.2456</v>
       </c>
       <c r="J49" t="n">
-        <v>12.2892</v>
+        <v>10.3152</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.158</v>
+        <v>0.126</v>
       </c>
       <c r="J50" t="n">
-        <v>6.636</v>
+        <v>5.292</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1331</v>
+        <v>-0.1139</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.5902</v>
+        <v>-4.7838</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3207</v>
+        <v>0.3104</v>
       </c>
       <c r="J52" t="n">
-        <v>8.0175</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.08</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1725</v>
+        <v>0.1552</v>
       </c>
       <c r="J53" t="n">
-        <v>4.3125</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0405</v>
+        <v>-0.0314</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.0125</v>
+        <v>-0.785</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1656</v>
+        <v>-0.1458</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.14</v>
+        <v>-3.645</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3713</v>
+        <v>-0.358</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.282500000000001</v>
+        <v>-8.949999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.62</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6632</v>
+        <v>0.6207</v>
       </c>
       <c r="J57" t="n">
-        <v>16.58</v>
+        <v>15.5175</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3214</v>
+        <v>0.267</v>
       </c>
       <c r="J58" t="n">
-        <v>8.035</v>
+        <v>6.675</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.14</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2236</v>
+        <v>0.1803</v>
       </c>
       <c r="J59" t="n">
-        <v>5.59</v>
+        <v>4.5075</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.13</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2103</v>
+        <v>0.1687</v>
       </c>
       <c r="J60" t="n">
-        <v>5.2575</v>
+        <v>4.2175</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.0607</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.8725</v>
+        <v>-1.5175</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.44</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8694</v>
+        <v>0.8542</v>
       </c>
       <c r="J62" t="n">
-        <v>34.776</v>
+        <v>34.168</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.35</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7415</v>
+        <v>0.7271</v>
       </c>
       <c r="J63" t="n">
-        <v>29.66</v>
+        <v>29.084</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5929</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>23.716</v>
+        <v>23.368</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.07</v>
       </c>
       <c r="I65" t="n">
-        <v>0.225</v>
+        <v>0.1956</v>
       </c>
       <c r="J65" t="n">
-        <v>9</v>
+        <v>7.824</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0374</v>
+        <v>-0.0319</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.496</v>
+        <v>-1.276</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.23</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4793</v>
+        <v>0.4354</v>
       </c>
       <c r="J67" t="n">
-        <v>19.172</v>
+        <v>17.416</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0233</v>
+        <v>-0.0172</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.6879999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1087</v>
+        <v>-0.0917</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.348</v>
+        <v>-3.668</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.85</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1982</v>
+        <v>-0.1778</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.928</v>
+        <v>-7.112</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2291</v>
+        <v>-0.2087</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.164</v>
+        <v>-8.348000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.03</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1059</v>
+        <v>0.0779</v>
       </c>
       <c r="J72" t="n">
-        <v>4.3419</v>
+        <v>3.1939</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0043</v>
+        <v>0.0023</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1763</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0561</v>
+        <v>-0.0446</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.3001</v>
+        <v>-1.8286</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0961</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.9401</v>
+        <v>-3.2882</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1873</v>
+        <v>-0.167</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.6793</v>
+        <v>-6.847</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.47</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0699</v>
+        <v>1.0782</v>
       </c>
       <c r="J77" t="n">
-        <v>43.8659</v>
+        <v>44.2062</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.18</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5051</v>
+        <v>0.4687</v>
       </c>
       <c r="J78" t="n">
-        <v>20.7091</v>
+        <v>19.2167</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5051</v>
+        <v>0.4687</v>
       </c>
       <c r="J79" t="n">
-        <v>20.7091</v>
+        <v>19.2167</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2623</v>
+        <v>0.2305</v>
       </c>
       <c r="J80" t="n">
-        <v>10.7543</v>
+        <v>9.4505</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.92</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3195</v>
+        <v>-0.2786</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.0995</v>
+        <v>-11.4226</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2055</v>
+        <v>0.1634</v>
       </c>
       <c r="J82" t="n">
-        <v>5.343</v>
+        <v>4.2484</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1118</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>2.9068</v>
+        <v>2.1476</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.03</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1118</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>2.9068</v>
+        <v>2.1476</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1845</v>
+        <v>-0.1646</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.797</v>
+        <v>-4.2796</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.65</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3865</v>
+        <v>-0.3744</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.049</v>
+        <v>-9.734400000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>1.143</v>
+        <v>1.1564</v>
       </c>
       <c r="J87" t="n">
-        <v>29.718</v>
+        <v>30.0664</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7218</v>
+        <v>0.6912</v>
       </c>
       <c r="J88" t="n">
-        <v>18.7668</v>
+        <v>17.9712</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2078</v>
+        <v>0.1787</v>
       </c>
       <c r="J89" t="n">
-        <v>5.4028</v>
+        <v>4.6462</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.02</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0761</v>
+        <v>0.0595</v>
       </c>
       <c r="J90" t="n">
-        <v>1.9786</v>
+        <v>1.547</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4237</v>
+        <v>-0.3818</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.0162</v>
+        <v>-9.9268</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.52</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9352</v>
+        <v>0.8962</v>
       </c>
       <c r="J92" t="n">
-        <v>25.2504</v>
+        <v>24.1974</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1953</v>
+        <v>0.1546</v>
       </c>
       <c r="J93" t="n">
-        <v>5.2731</v>
+        <v>4.1742</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1995</v>
+        <v>-0.1789</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.3865</v>
+        <v>-4.8303</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2099</v>
+        <v>-0.1893</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.6673</v>
+        <v>-5.1111</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.61</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4266</v>
+        <v>-0.4189</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.5182</v>
+        <v>-11.3103</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8262</v>
+        <v>0.8021</v>
       </c>
       <c r="J97" t="n">
-        <v>22.3074</v>
+        <v>21.6567</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5744</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>15.5088</v>
+        <v>14.5206</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.15</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4399</v>
+        <v>0.4025</v>
       </c>
       <c r="J99" t="n">
-        <v>11.8773</v>
+        <v>10.8675</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3445</v>
+        <v>0.3089</v>
       </c>
       <c r="J100" t="n">
-        <v>9.301500000000001</v>
+        <v>8.340299999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3154</v>
+        <v>-0.2743</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.5158</v>
+        <v>-7.4061</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5561</v>
+        <v>0.4994</v>
       </c>
       <c r="J102" t="n">
-        <v>13.9025</v>
+        <v>12.485</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0813</v>
+        <v>-0.0677</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.0325</v>
+        <v>-1.6925</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.92</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.118</v>
+        <v>-0.1013</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.95</v>
+        <v>-2.5325</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2152</v>
+        <v>-0.195</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.38</v>
+        <v>-4.875</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3771</v>
+        <v>-0.3641</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.4275</v>
+        <v>-9.102499999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7836</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>19.59</v>
+        <v>18.915</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.701</v>
+        <v>0.6693</v>
       </c>
       <c r="J108" t="n">
-        <v>17.525</v>
+        <v>16.7325</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5511</v>
+        <v>0.5145</v>
       </c>
       <c r="J109" t="n">
-        <v>13.7775</v>
+        <v>12.8625</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4844</v>
+        <v>0.4473</v>
       </c>
       <c r="J110" t="n">
-        <v>12.11</v>
+        <v>11.1825</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.594</v>
+        <v>-0.5572</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.85</v>
+        <v>-13.93</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9691</v>
+        <v>0.9608</v>
       </c>
       <c r="J112" t="n">
-        <v>22.2893</v>
+        <v>22.0984</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.61</v>
+        <v>0.5765</v>
       </c>
       <c r="J113" t="n">
-        <v>14.03</v>
+        <v>13.2595</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.19</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4898</v>
       </c>
       <c r="J114" t="n">
-        <v>12.0681</v>
+        <v>11.2654</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.07</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2303</v>
+        <v>0.2005</v>
       </c>
       <c r="J115" t="n">
-        <v>5.2969</v>
+        <v>4.6115</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.05</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1712</v>
+        <v>0.1449</v>
       </c>
       <c r="J116" t="n">
-        <v>3.9376</v>
+        <v>3.3327</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.04</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1456</v>
+        <v>0.1116</v>
       </c>
       <c r="J117" t="n">
-        <v>3.3488</v>
+        <v>2.5668</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.93</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1039</v>
+        <v>-0.089</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.3897</v>
+        <v>-2.047</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.85</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1916</v>
+        <v>-0.1723</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.4068</v>
+        <v>-3.9629</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2019</v>
+        <v>-0.1824</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.6437</v>
+        <v>-4.1952</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2518</v>
+        <v>-0.2324</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.7914</v>
+        <v>-5.3452</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9489</v>
       </c>
       <c r="J122" t="n">
-        <v>26.8576</v>
+        <v>26.5692</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8628</v>
+        <v>0.8418</v>
       </c>
       <c r="J123" t="n">
-        <v>24.1584</v>
+        <v>23.5704</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5937</v>
+        <v>0.5582</v>
       </c>
       <c r="J124" t="n">
-        <v>16.6236</v>
+        <v>15.6296</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.12</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3674</v>
+        <v>0.3319</v>
       </c>
       <c r="J125" t="n">
-        <v>10.2872</v>
+        <v>9.293200000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.8204</v>
       </c>
       <c r="J126" t="n">
-        <v>-23.4696</v>
+        <v>-22.9712</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5123</v>
+        <v>0.4563</v>
       </c>
       <c r="J127" t="n">
-        <v>14.3444</v>
+        <v>12.7764</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.95</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0796</v>
+        <v>-0.0665</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.2288</v>
+        <v>-1.862</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1051</v>
+        <v>-0.0898</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.9428</v>
+        <v>-2.5144</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.73</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3107</v>
+        <v>-0.2931</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.6996</v>
+        <v>-8.206799999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.357</v>
+        <v>-0.3423</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.996</v>
+        <v>-9.5844</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3383</v>
+        <v>0.2852</v>
       </c>
       <c r="J132" t="n">
-        <v>10.149</v>
+        <v>8.555999999999999</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0226</v>
+        <v>-0.0167</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.678</v>
+        <v>-0.501</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.92</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.12</v>
+        <v>-0.1024</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.6</v>
+        <v>-3.072</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.88</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1653</v>
+        <v>-0.1455</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.959</v>
+        <v>-4.365</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.84</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2077</v>
+        <v>-0.1873</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.231</v>
+        <v>-5.619</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.53</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1605</v>
+        <v>1.1748</v>
       </c>
       <c r="J137" t="n">
-        <v>34.815</v>
+        <v>35.244</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.52</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1466</v>
+        <v>1.1604</v>
       </c>
       <c r="J138" t="n">
-        <v>34.398</v>
+        <v>34.812</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3143</v>
+        <v>-0.2732</v>
       </c>
       <c r="J139" t="n">
-        <v>-9.429</v>
+        <v>-8.196</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4466</v>
+        <v>-0.4046</v>
       </c>
       <c r="J140" t="n">
-        <v>-13.398</v>
+        <v>-12.138</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.85</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4962</v>
+        <v>-0.4552</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.886</v>
+        <v>-13.656</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4954</v>
+        <v>0.4373</v>
       </c>
       <c r="J142" t="n">
-        <v>16.8436</v>
+        <v>14.8682</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.08</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2202</v>
+        <v>0.1765</v>
       </c>
       <c r="J143" t="n">
-        <v>7.4868</v>
+        <v>6.001</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.99</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0229</v>
+        <v>-0.0169</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.7786</v>
+        <v>-0.5746</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0959</v>
+        <v>-0.0801</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.2606</v>
+        <v>-2.7234</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.55</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4771</v>
+        <v>-0.4752</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.2214</v>
+        <v>-16.1568</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7027</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>23.8918</v>
+        <v>22.8106</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6178</v>
+        <v>0.5824</v>
       </c>
       <c r="J148" t="n">
-        <v>21.0052</v>
+        <v>19.8016</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5962</v>
+        <v>0.5602</v>
       </c>
       <c r="J149" t="n">
-        <v>20.2708</v>
+        <v>19.0468</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.12</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3693</v>
+        <v>0.333</v>
       </c>
       <c r="J150" t="n">
-        <v>12.5562</v>
+        <v>11.322</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4223</v>
+        <v>-0.3802</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.3582</v>
+        <v>-12.9268</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.91</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0774</v>
+        <v>-0.0562</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.548</v>
+        <v>-1.124</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.7</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3078</v>
+        <v>-0.2964</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.156</v>
+        <v>-5.928</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.61</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3877</v>
+        <v>-0.3784</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.754</v>
+        <v>-7.568</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4836</v>
+        <v>-0.4801</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.672000000000001</v>
+        <v>-9.602</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.4</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5716</v>
+        <v>-0.5789</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.432</v>
+        <v>-11.578</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.89</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5451</v>
+        <v>1.5799</v>
       </c>
       <c r="J157" t="n">
-        <v>30.902</v>
+        <v>31.598</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.63</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2291</v>
+        <v>1.2478</v>
       </c>
       <c r="J158" t="n">
-        <v>24.582</v>
+        <v>24.956</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.53</v>
       </c>
       <c r="I159" t="n">
-        <v>1.103</v>
+        <v>1.1196</v>
       </c>
       <c r="J159" t="n">
-        <v>22.06</v>
+        <v>22.392</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.36</v>
       </c>
       <c r="I160" t="n">
-        <v>0.8348</v>
+        <v>0.825</v>
       </c>
       <c r="J160" t="n">
-        <v>16.696</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3095</v>
+        <v>-0.2784</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.19</v>
+        <v>-5.568</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.92</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0663</v>
+        <v>-0.0454</v>
       </c>
       <c r="J162" t="n">
-        <v>-1.5249</v>
+        <v>-1.0442</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.71</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2993</v>
+        <v>-0.2875</v>
       </c>
       <c r="J163" t="n">
-        <v>-6.8839</v>
+        <v>-6.6125</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.63</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3716</v>
+        <v>-0.3617</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.546799999999999</v>
+        <v>-8.319100000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.53</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4581</v>
+        <v>-0.4523</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.5363</v>
+        <v>-10.4029</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.36</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6075</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.9725</v>
+        <v>-14.2715</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.84</v>
       </c>
       <c r="I167" t="n">
-        <v>1.4814</v>
+        <v>1.5119</v>
       </c>
       <c r="J167" t="n">
-        <v>34.0722</v>
+        <v>34.7737</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.71</v>
       </c>
       <c r="I168" t="n">
-        <v>1.3247</v>
+        <v>1.347</v>
       </c>
       <c r="J168" t="n">
-        <v>30.4681</v>
+        <v>30.981</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7932</v>
+        <v>0.7811</v>
       </c>
       <c r="J169" t="n">
-        <v>18.2436</v>
+        <v>17.9653</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.29</v>
       </c>
       <c r="I170" t="n">
-        <v>0.6942</v>
+        <v>0.6755</v>
       </c>
       <c r="J170" t="n">
-        <v>15.9666</v>
+        <v>15.5365</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.29</v>
       </c>
       <c r="I171" t="n">
-        <v>0.6942</v>
+        <v>0.6755</v>
       </c>
       <c r="J171" t="n">
-        <v>15.9666</v>
+        <v>15.5365</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.2</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3617</v>
+        <v>0.357</v>
       </c>
       <c r="J172" t="n">
-        <v>9.0425</v>
+        <v>8.925000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.02</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0708</v>
+        <v>0.0575</v>
       </c>
       <c r="J173" t="n">
-        <v>1.77</v>
+        <v>1.4375</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.243</v>
+        <v>-0.2233</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.075</v>
+        <v>-5.5825</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.75</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2914</v>
+        <v>-0.2729</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.285</v>
+        <v>-6.8225</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3103</v>
+        <v>-0.2927</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.7575</v>
+        <v>-7.3175</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.39</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5105</v>
+        <v>0.4421</v>
       </c>
       <c r="J177" t="n">
-        <v>12.7625</v>
+        <v>11.0525</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5105</v>
+        <v>0.4421</v>
       </c>
       <c r="J178" t="n">
-        <v>12.7625</v>
+        <v>11.0525</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1555</v>
+        <v>0.1214</v>
       </c>
       <c r="J179" t="n">
-        <v>3.8875</v>
+        <v>3.035</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.08</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1406</v>
+        <v>0.1088</v>
       </c>
       <c r="J180" t="n">
-        <v>3.515</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.06</v>
       </c>
       <c r="I181" t="n">
-        <v>0.1094</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>2.735</v>
+        <v>2.065</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.371</v>
+        <v>1.3943</v>
       </c>
       <c r="J182" t="n">
-        <v>35.646</v>
+        <v>36.2518</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0281</v>
+        <v>1.032</v>
       </c>
       <c r="J183" t="n">
-        <v>26.7306</v>
+        <v>26.832</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.41</v>
       </c>
       <c r="I184" t="n">
-        <v>0.9462</v>
+        <v>0.9378</v>
       </c>
       <c r="J184" t="n">
-        <v>24.6012</v>
+        <v>24.3828</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.01</v>
       </c>
       <c r="I185" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="J185" t="n">
-        <v>0.2262</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3429</v>
+        <v>-0.3052</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.9154</v>
+        <v>-7.9352</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.88</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.15</v>
+        <v>-0.1344</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.9</v>
+        <v>-3.4944</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.82</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2136</v>
+        <v>-0.197</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.5536</v>
+        <v>-5.122</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2427</v>
+        <v>-0.2257</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.3102</v>
+        <v>-5.8682</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3074</v>
+        <v>-0.2909</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.9924</v>
+        <v>-7.5634</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.71</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3166</v>
+        <v>-0.3004</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.2316</v>
+        <v>-7.8104</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.66</v>
+        <v>0.6242</v>
       </c>
       <c r="J192" t="n">
-        <v>17.82</v>
+        <v>16.8534</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.16</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4781</v>
+        <v>0.4367</v>
       </c>
       <c r="J193" t="n">
-        <v>12.9087</v>
+        <v>11.7909</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3298</v>
+        <v>0.2904</v>
       </c>
       <c r="J194" t="n">
-        <v>8.9046</v>
+        <v>7.8408</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.06</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2212</v>
+        <v>0.1878</v>
       </c>
       <c r="J195" t="n">
-        <v>5.9724</v>
+        <v>5.0706</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.73</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7559</v>
+        <v>-0.728</v>
       </c>
       <c r="J196" t="n">
-        <v>-20.4093</v>
+        <v>-19.656</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7739</v>
+        <v>0.7184</v>
       </c>
       <c r="J197" t="n">
-        <v>20.8953</v>
+        <v>19.3968</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.32</v>
       </c>
       <c r="I198" t="n">
-        <v>0.61</v>
+        <v>0.5502</v>
       </c>
       <c r="J198" t="n">
-        <v>16.47</v>
+        <v>14.8554</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.91</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1415</v>
+        <v>-0.1219</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.8205</v>
+        <v>-3.2913</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1415</v>
+        <v>-0.1219</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.8205</v>
+        <v>-3.2913</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.79</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2686</v>
+        <v>-0.2496</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.2522</v>
+        <v>-6.7392</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5239</v>
+        <v>0.4671</v>
       </c>
       <c r="J202" t="n">
-        <v>13.6214</v>
+        <v>12.1446</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.02</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0861</v>
+        <v>0.0617</v>
       </c>
       <c r="J203" t="n">
-        <v>2.2386</v>
+        <v>1.6042</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0939</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.4414</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.83</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2148</v>
+        <v>-0.1947</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.5848</v>
+        <v>-5.0622</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4565</v>
+        <v>-0.4516</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.869</v>
+        <v>-11.7416</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.41</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9512</v>
       </c>
       <c r="J207" t="n">
-        <v>24.9652</v>
+        <v>24.7312</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7875</v>
+        <v>0.7635</v>
       </c>
       <c r="J208" t="n">
-        <v>20.475</v>
+        <v>19.851</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7275</v>
+        <v>0.7005</v>
       </c>
       <c r="J209" t="n">
-        <v>18.915</v>
+        <v>18.213</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.24</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6258</v>
+        <v>0.5951</v>
       </c>
       <c r="J210" t="n">
-        <v>16.2708</v>
+        <v>15.4726</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.89</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4116</v>
+        <v>-0.3714</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.7016</v>
+        <v>-9.6564</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3999</v>
+        <v>0.3444</v>
       </c>
       <c r="J212" t="n">
-        <v>11.1972</v>
+        <v>9.6432</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1118</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>3.1304</v>
+        <v>2.3128</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1182</v>
+        <v>-0.1014</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.3096</v>
+        <v>-2.8392</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1949</v>
+        <v>-0.1749</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.4572</v>
+        <v>-4.8972</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.67</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3684</v>
+        <v>-0.3548</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.3152</v>
+        <v>-9.9344</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.45</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0367</v>
+        <v>1.04</v>
       </c>
       <c r="J217" t="n">
-        <v>29.0276</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.29</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7361</v>
+        <v>0.7074</v>
       </c>
       <c r="J218" t="n">
-        <v>20.6108</v>
+        <v>19.8072</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.14</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4125</v>
+        <v>0.3773</v>
       </c>
       <c r="J219" t="n">
-        <v>11.55</v>
+        <v>10.5644</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0708</v>
+        <v>0.0545</v>
       </c>
       <c r="J220" t="n">
-        <v>1.9824</v>
+        <v>1.526</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.01</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0294</v>
+        <v>0.0196</v>
       </c>
       <c r="J221" t="n">
-        <v>0.8232</v>
+        <v>0.5488</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.21</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5879</v>
+        <v>0.5493</v>
       </c>
       <c r="J222" t="n">
-        <v>16.4612</v>
+        <v>15.3804</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4734</v>
+        <v>0.4327</v>
       </c>
       <c r="J223" t="n">
-        <v>13.2552</v>
+        <v>12.1156</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.16</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4734</v>
+        <v>0.4327</v>
       </c>
       <c r="J224" t="n">
-        <v>13.2552</v>
+        <v>12.1156</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0475</v>
+        <v>0.0357</v>
       </c>
       <c r="J225" t="n">
-        <v>1.33</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.86</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4605</v>
+        <v>-0.4179</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.894</v>
+        <v>-11.7012</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.29</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5793</v>
+        <v>0.5201</v>
       </c>
       <c r="J227" t="n">
-        <v>16.2204</v>
+        <v>14.5628</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.19</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4148</v>
+        <v>0.3579</v>
       </c>
       <c r="J228" t="n">
-        <v>11.6144</v>
+        <v>10.0212</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2511</v>
+        <v>0.2048</v>
       </c>
       <c r="J229" t="n">
-        <v>7.0308</v>
+        <v>5.7344</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1122</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.1416</v>
+        <v>-2.6404</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4981</v>
+        <v>-0.4997</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.9468</v>
+        <v>-13.9916</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.51</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1145</v>
+        <v>1.1264</v>
       </c>
       <c r="J232" t="n">
-        <v>28.977</v>
+        <v>29.2864</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.5</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1009</v>
+        <v>1.1121</v>
       </c>
       <c r="J233" t="n">
-        <v>28.6234</v>
+        <v>28.9146</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.09</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2812</v>
+        <v>0.2495</v>
       </c>
       <c r="J234" t="n">
-        <v>7.3112</v>
+        <v>6.487</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.5012</v>
+        <v>-1.9604</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.99</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J236" t="n">
-        <v>-2.5012</v>
+        <v>-1.9604</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.05</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1707</v>
+        <v>0.1333</v>
       </c>
       <c r="J237" t="n">
-        <v>4.4382</v>
+        <v>3.4658</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.92</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1156</v>
+        <v>-0.1</v>
       </c>
       <c r="J238" t="n">
-        <v>-3.0056</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1386</v>
+        <v>-0.1215</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.6036</v>
+        <v>-3.159</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2217</v>
+        <v>-0.2022</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.7642</v>
+        <v>-5.2572</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.74</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2994</v>
+        <v>-0.2814</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.7844</v>
+        <v>-7.3164</v>
       </c>
     </row>
   </sheetData>
